--- a/hw04/hw04/microcode.xlsx
+++ b/hw04/hw04/microcode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huan\Documents\GT\Summer 2023\CS_2110\hw04\hw04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9AC8E8-AABF-4C3E-B254-96C4A97C3047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8226AA-6308-4314-B537-5AE4B82ECD00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -617,7 +617,7 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" textRotation="45"/>
@@ -639,7 +639,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1116,100 +1115,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:75" ht="88">
-      <c r="A1" s="40"/>
-      <c r="B1" s="41"/>
-      <c r="C1" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="54" t="s">
+      <c r="A1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="H1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="I1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="55" t="s">
+      <c r="J1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="55" t="s">
+      <c r="K1" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="55" t="s">
+      <c r="L1" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="56" t="s">
+      <c r="M1" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="42" t="s">
+      <c r="N1" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="57" t="s">
+      <c r="O1" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="57" t="s">
+      <c r="P1" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="56" t="s">
+      <c r="Q1" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="56" t="s">
+      <c r="R1" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="42" t="s">
+      <c r="S1" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="56" t="s">
+      <c r="T1" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="56" t="s">
+      <c r="U1" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="42" t="s">
+      <c r="V1" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="W1" s="58" t="s">
+      <c r="W1" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="58" t="s">
+      <c r="X1" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="59" t="s">
+      <c r="Y1" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="43" t="s">
+      <c r="Z1" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="AA1" s="44" t="s">
+      <c r="AA1" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="44" t="s">
+      <c r="AB1" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="AC1" s="44" t="s">
+      <c r="AC1" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="38" t="s">
+      <c r="AD1" s="37" t="s">
         <v>21</v>
       </c>
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
     </row>
     <row r="2" spans="1:75" ht="31">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="45"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
@@ -1221,9 +1220,9 @@
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
       <c r="M2" s="14"/>
-      <c r="N2" s="63"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="36"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="35"/>
       <c r="Q2" s="14"/>
       <c r="R2" s="14"/>
       <c r="S2" s="9"/>
@@ -1231,19 +1230,19 @@
       <c r="U2" s="14"/>
       <c r="V2" s="9"/>
       <c r="W2" s="17"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="31"/>
-      <c r="AA2" s="31"/>
-      <c r="AB2" s="31"/>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="22"/>
+      <c r="X2" s="64"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="30"/>
+      <c r="AC2" s="30"/>
+      <c r="AD2" s="21"/>
       <c r="AH2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:75" ht="32.15" customHeight="1">
-      <c r="A3" s="49"/>
+      <c r="A3" s="48"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -1255,26 +1254,26 @@
       <c r="K3" s="13"/>
       <c r="L3" s="13"/>
       <c r="M3" s="15"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="36"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="35"/>
       <c r="Q3" s="15"/>
       <c r="R3" s="15"/>
-      <c r="S3" s="30"/>
+      <c r="S3" s="29"/>
       <c r="T3" s="15"/>
       <c r="U3" s="15"/>
-      <c r="V3" s="30"/>
+      <c r="V3" s="29"/>
       <c r="W3" s="18"/>
-      <c r="X3" s="66"/>
-      <c r="Y3" s="31"/>
-      <c r="Z3" s="31"/>
-      <c r="AA3" s="31"/>
-      <c r="AB3" s="31"/>
-      <c r="AC3" s="31"/>
-      <c r="AD3" s="22"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="30"/>
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="21"/>
     </row>
     <row r="4" spans="1:75">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="48" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="11">
@@ -1310,13 +1309,13 @@
       <c r="M4" s="15">
         <v>0</v>
       </c>
-      <c r="N4" s="64">
-        <v>0</v>
-      </c>
-      <c r="O4" s="37">
-        <v>0</v>
-      </c>
-      <c r="P4" s="36">
+      <c r="N4" s="63">
+        <v>0</v>
+      </c>
+      <c r="O4" s="36">
+        <v>0</v>
+      </c>
+      <c r="P4" s="35">
         <v>0</v>
       </c>
       <c r="Q4" s="15">
@@ -1325,7 +1324,7 @@
       <c r="R4" s="15">
         <v>0</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="29">
         <v>0</v>
       </c>
       <c r="T4" s="15">
@@ -1334,38 +1333,38 @@
       <c r="U4" s="15">
         <v>0</v>
       </c>
-      <c r="V4" s="30">
+      <c r="V4" s="29">
         <v>0</v>
       </c>
       <c r="W4" s="18">
         <v>0</v>
       </c>
-      <c r="X4" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="31">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="22">
+      <c r="X4" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="21">
         <v>0</v>
       </c>
       <c r="BQ4" s="1"/>
       <c r="BR4" s="1"/>
     </row>
     <row r="5" spans="1:75">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="48" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="11">
@@ -1401,13 +1400,13 @@
       <c r="M5" s="15">
         <v>0</v>
       </c>
-      <c r="N5" s="64">
-        <v>0</v>
-      </c>
-      <c r="O5" s="37">
-        <v>0</v>
-      </c>
-      <c r="P5" s="36">
+      <c r="N5" s="63">
+        <v>0</v>
+      </c>
+      <c r="O5" s="36">
+        <v>0</v>
+      </c>
+      <c r="P5" s="35">
         <v>0</v>
       </c>
       <c r="Q5" s="15">
@@ -1416,7 +1415,7 @@
       <c r="R5" s="15">
         <v>0</v>
       </c>
-      <c r="S5" s="30">
+      <c r="S5" s="29">
         <v>0</v>
       </c>
       <c r="T5" s="15">
@@ -1425,31 +1424,31 @@
       <c r="U5" s="15">
         <v>0</v>
       </c>
-      <c r="V5" s="30">
+      <c r="V5" s="29">
         <v>0</v>
       </c>
       <c r="W5" s="18">
         <v>1</v>
       </c>
-      <c r="X5" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="31">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="22">
+      <c r="X5" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="21">
         <v>0</v>
       </c>
       <c r="AH5" t="str">
@@ -1458,7 +1457,7 @@
       </c>
     </row>
     <row r="6" spans="1:75">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="48" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="11">
@@ -1494,13 +1493,13 @@
       <c r="M6" s="15">
         <v>0</v>
       </c>
-      <c r="N6" s="64">
-        <v>0</v>
-      </c>
-      <c r="O6" s="76">
-        <v>0</v>
-      </c>
-      <c r="P6" s="36">
+      <c r="N6" s="63">
+        <v>0</v>
+      </c>
+      <c r="O6" s="75">
+        <v>0</v>
+      </c>
+      <c r="P6" s="35">
         <v>0</v>
       </c>
       <c r="Q6" s="15">
@@ -1509,7 +1508,7 @@
       <c r="R6" s="15">
         <v>0</v>
       </c>
-      <c r="S6" s="30">
+      <c r="S6" s="29">
         <v>0</v>
       </c>
       <c r="T6" s="15">
@@ -1518,31 +1517,31 @@
       <c r="U6" s="15">
         <v>0</v>
       </c>
-      <c r="V6" s="30">
+      <c r="V6" s="29">
         <v>0</v>
       </c>
       <c r="W6" s="18">
         <v>0</v>
       </c>
-      <c r="X6" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="31">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="22">
+      <c r="X6" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="21">
         <v>0</v>
       </c>
       <c r="AH6" t="str">
@@ -1551,182 +1550,182 @@
       </c>
     </row>
     <row r="7" spans="1:75" ht="31">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="48"/>
-      <c r="W7" s="24"/>
-      <c r="X7" s="71"/>
-      <c r="Y7" s="20"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="20"/>
-      <c r="AB7" s="20"/>
-      <c r="AC7" s="20"/>
-      <c r="AD7" s="21"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="23"/>
+      <c r="V7" s="47"/>
+      <c r="W7" s="23"/>
+      <c r="X7" s="70"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
+      <c r="AA7" s="19"/>
+      <c r="AB7" s="19"/>
+      <c r="AC7" s="19"/>
+      <c r="AD7" s="20"/>
       <c r="AH7" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C6:F6), 1), BIN2HEX(_xlfn.CONCAT(G6:N6), 2), BIN2HEX(_xlfn.CONCAT(O6:V6), 2), BIN2HEX(_xlfn.CONCAT(W6:AD6), 2) )</f>
         <v>2100038</v>
       </c>
     </row>
     <row r="8" spans="1:75" ht="32.15" customHeight="1">
-      <c r="A8" s="49"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
-      <c r="S8" s="36"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="25"/>
-      <c r="V8" s="36"/>
-      <c r="W8" s="25"/>
-      <c r="X8" s="72"/>
-      <c r="Y8" s="31"/>
-      <c r="Z8" s="31"/>
-      <c r="AA8" s="31"/>
-      <c r="AB8" s="31"/>
-      <c r="AC8" s="31"/>
-      <c r="AD8" s="22"/>
+      <c r="A8" s="48"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="24"/>
+      <c r="X8" s="71"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="30"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="21"/>
     </row>
     <row r="9" spans="1:75">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="69">
-        <v>0</v>
-      </c>
-      <c r="D9" s="69">
-        <v>0</v>
-      </c>
-      <c r="E9" s="69">
-        <v>0</v>
-      </c>
-      <c r="F9" s="69">
-        <v>0</v>
-      </c>
-      <c r="G9" s="69">
-        <v>0</v>
-      </c>
-      <c r="H9" s="69">
-        <v>0</v>
-      </c>
-      <c r="I9" s="25">
-        <v>0</v>
-      </c>
-      <c r="J9" s="25">
-        <v>0</v>
-      </c>
-      <c r="K9" s="25">
-        <v>0</v>
-      </c>
-      <c r="L9" s="25">
-        <v>0</v>
-      </c>
-      <c r="M9" s="70">
-        <v>0</v>
-      </c>
-      <c r="N9" s="75">
-        <v>0</v>
-      </c>
-      <c r="O9" s="35">
-        <v>0</v>
-      </c>
-      <c r="P9" s="69">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="69">
-        <v>0</v>
-      </c>
-      <c r="R9" s="69">
-        <v>0</v>
-      </c>
-      <c r="S9" s="35">
-        <v>0</v>
-      </c>
-      <c r="T9" s="69">
-        <v>0</v>
-      </c>
-      <c r="U9" s="69">
-        <v>0</v>
-      </c>
-      <c r="V9" s="35">
-        <v>0</v>
-      </c>
-      <c r="W9" s="69">
-        <v>0</v>
-      </c>
-      <c r="X9" s="72">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="31">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="22">
+      <c r="C9" s="68">
+        <v>0</v>
+      </c>
+      <c r="D9" s="68">
+        <v>0</v>
+      </c>
+      <c r="E9" s="68">
+        <v>0</v>
+      </c>
+      <c r="F9" s="68">
+        <v>0</v>
+      </c>
+      <c r="G9" s="68">
+        <v>0</v>
+      </c>
+      <c r="H9" s="68">
+        <v>0</v>
+      </c>
+      <c r="I9" s="24">
+        <v>0</v>
+      </c>
+      <c r="J9" s="24">
+        <v>0</v>
+      </c>
+      <c r="K9" s="24">
+        <v>0</v>
+      </c>
+      <c r="L9" s="24">
+        <v>0</v>
+      </c>
+      <c r="M9" s="69">
+        <v>0</v>
+      </c>
+      <c r="N9" s="74">
+        <v>0</v>
+      </c>
+      <c r="O9" s="34">
+        <v>0</v>
+      </c>
+      <c r="P9" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="68">
+        <v>0</v>
+      </c>
+      <c r="R9" s="68">
+        <v>0</v>
+      </c>
+      <c r="S9" s="34">
+        <v>0</v>
+      </c>
+      <c r="T9" s="68">
+        <v>0</v>
+      </c>
+      <c r="U9" s="68">
+        <v>0</v>
+      </c>
+      <c r="V9" s="34">
+        <v>0</v>
+      </c>
+      <c r="W9" s="68">
+        <v>0</v>
+      </c>
+      <c r="X9" s="71">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:75" ht="31">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
       <c r="L10" s="12"/>
       <c r="M10" s="15"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
       <c r="Q10" s="14"/>
       <c r="R10" s="14"/>
       <c r="S10" s="9"/>
@@ -1734,69 +1733,69 @@
       <c r="U10" s="14"/>
       <c r="V10" s="9"/>
       <c r="W10" s="17"/>
-      <c r="X10" s="65"/>
-      <c r="Y10" s="20"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="20"/>
-      <c r="AB10" s="20"/>
-      <c r="AC10" s="20"/>
-      <c r="AD10" s="21"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="19"/>
+      <c r="AA10" s="19"/>
+      <c r="AB10" s="19"/>
+      <c r="AC10" s="19"/>
+      <c r="AD10" s="20"/>
       <c r="AH10" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C9:F9), 1), BIN2HEX(_xlfn.CONCAT(G9:N9), 2), BIN2HEX(_xlfn.CONCAT(O9:V9), 2), BIN2HEX(_xlfn.CONCAT(W9:AD9), 2) )</f>
         <v>0000020</v>
       </c>
     </row>
     <row r="11" spans="1:75" ht="32.15" customHeight="1">
-      <c r="A11" s="50"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
+      <c r="A11" s="49"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
       <c r="M11" s="15"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="25"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
       <c r="Q11" s="15"/>
       <c r="R11" s="15"/>
-      <c r="S11" s="30"/>
+      <c r="S11" s="29"/>
       <c r="T11" s="15"/>
       <c r="U11" s="15"/>
-      <c r="V11" s="30"/>
+      <c r="V11" s="29"/>
       <c r="W11" s="18"/>
-      <c r="X11" s="66"/>
-      <c r="Y11" s="31"/>
-      <c r="Z11" s="31"/>
-      <c r="AA11" s="31"/>
-      <c r="AB11" s="31"/>
-      <c r="AC11" s="31"/>
-      <c r="AD11" s="22"/>
+      <c r="X11" s="65"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+      <c r="AA11" s="30"/>
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="30"/>
+      <c r="AD11" s="21"/>
     </row>
     <row r="12" spans="1:75" ht="16" customHeight="1">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="60">
-        <v>0</v>
-      </c>
-      <c r="D12" s="60">
-        <v>0</v>
-      </c>
-      <c r="E12" s="60">
-        <v>0</v>
-      </c>
-      <c r="F12" s="60">
-        <v>1</v>
-      </c>
-      <c r="G12" s="60">
-        <v>1</v>
-      </c>
-      <c r="H12" s="60">
+      <c r="C12" s="59">
+        <v>0</v>
+      </c>
+      <c r="D12" s="59">
+        <v>0</v>
+      </c>
+      <c r="E12" s="59">
+        <v>0</v>
+      </c>
+      <c r="F12" s="59">
+        <v>1</v>
+      </c>
+      <c r="G12" s="59">
+        <v>1</v>
+      </c>
+      <c r="H12" s="59">
         <v>0</v>
       </c>
       <c r="I12" s="13">
@@ -1814,13 +1813,13 @@
       <c r="M12" s="15">
         <v>0</v>
       </c>
-      <c r="N12" s="30">
-        <v>0</v>
-      </c>
-      <c r="O12" s="26">
-        <v>0</v>
-      </c>
-      <c r="P12" s="26">
+      <c r="N12" s="29">
+        <v>0</v>
+      </c>
+      <c r="O12" s="25">
+        <v>0</v>
+      </c>
+      <c r="P12" s="25">
         <v>1</v>
       </c>
       <c r="Q12" s="16">
@@ -1838,67 +1837,67 @@
       <c r="U12" s="15">
         <v>0</v>
       </c>
-      <c r="V12" s="30">
+      <c r="V12" s="29">
         <v>0</v>
       </c>
       <c r="W12" s="18">
         <v>0</v>
       </c>
-      <c r="X12" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="22">
+      <c r="X12" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:75" ht="31">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
       <c r="L13" s="12"/>
       <c r="M13" s="14"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="25"/>
-      <c r="P13" s="72"/>
-      <c r="Q13" s="30"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="29"/>
       <c r="R13" s="15"/>
-      <c r="S13" s="30"/>
+      <c r="S13" s="29"/>
       <c r="T13" s="14"/>
       <c r="U13" s="14"/>
       <c r="V13" s="9"/>
       <c r="W13" s="17"/>
-      <c r="X13" s="65"/>
-      <c r="Y13" s="20"/>
-      <c r="Z13" s="20"/>
-      <c r="AA13" s="20"/>
-      <c r="AB13" s="20"/>
-      <c r="AC13" s="20"/>
-      <c r="AD13" s="21"/>
+      <c r="X13" s="64"/>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="19"/>
+      <c r="AA13" s="19"/>
+      <c r="AB13" s="19"/>
+      <c r="AC13" s="19"/>
+      <c r="AD13" s="20"/>
       <c r="AH13" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C12:F12), 1), BIN2HEX(_xlfn.CONCAT(G12:N12), 2), BIN2HEX(_xlfn.CONCAT(O12:V12), 2), BIN2HEX(_xlfn.CONCAT(W12:AD12), 2) )</f>
         <v>188403F</v>
@@ -1943,35 +1942,35 @@
       <c r="BW13" s="4"/>
     </row>
     <row r="14" spans="1:75" ht="32.15" customHeight="1">
-      <c r="A14" s="49"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
+      <c r="A14" s="48"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
       <c r="L14" s="13"/>
       <c r="M14" s="15"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="30"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="29"/>
       <c r="R14" s="15"/>
-      <c r="S14" s="30"/>
+      <c r="S14" s="29"/>
       <c r="T14" s="15"/>
       <c r="U14" s="15"/>
-      <c r="V14" s="30"/>
+      <c r="V14" s="29"/>
       <c r="W14" s="18"/>
-      <c r="X14" s="66"/>
-      <c r="Y14" s="31"/>
-      <c r="Z14" s="31"/>
-      <c r="AA14" s="31"/>
-      <c r="AB14" s="31"/>
-      <c r="AC14" s="31"/>
-      <c r="AD14" s="22"/>
+      <c r="X14" s="65"/>
+      <c r="Y14" s="30"/>
+      <c r="Z14" s="30"/>
+      <c r="AA14" s="30"/>
+      <c r="AB14" s="30"/>
+      <c r="AC14" s="30"/>
+      <c r="AD14" s="21"/>
       <c r="AK14" s="3"/>
       <c r="AL14" s="4"/>
       <c r="AM14" s="4"/>
@@ -2013,7 +2012,7 @@
       <c r="BW14" s="4"/>
     </row>
     <row r="15" spans="1:75">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="48" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="11">
@@ -2049,22 +2048,22 @@
       <c r="M15" s="15">
         <v>0</v>
       </c>
-      <c r="N15" s="30">
-        <v>0</v>
-      </c>
-      <c r="O15" s="26">
-        <v>0</v>
-      </c>
-      <c r="P15" s="73">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="30">
+      <c r="N15" s="29">
+        <v>0</v>
+      </c>
+      <c r="O15" s="25">
+        <v>0</v>
+      </c>
+      <c r="P15" s="72">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="29">
         <v>0</v>
       </c>
       <c r="R15" s="15">
         <v>0</v>
       </c>
-      <c r="S15" s="30">
+      <c r="S15" s="29">
         <v>0</v>
       </c>
       <c r="T15" s="15">
@@ -2073,31 +2072,31 @@
       <c r="U15" s="15">
         <v>0</v>
       </c>
-      <c r="V15" s="30">
+      <c r="V15" s="29">
         <v>1</v>
       </c>
       <c r="W15" s="18">
         <v>0</v>
       </c>
-      <c r="X15" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD15" s="22">
+      <c r="X15" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="21">
         <v>1</v>
       </c>
       <c r="AK15" s="4"/>
@@ -2141,249 +2140,249 @@
       <c r="BW15" s="4"/>
     </row>
     <row r="16" spans="1:75" ht="31">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="72"/>
-      <c r="Q16" s="48"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="48"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="48"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="71"/>
-      <c r="Y16" s="20"/>
-      <c r="Z16" s="20"/>
-      <c r="AA16" s="20"/>
-      <c r="AB16" s="20"/>
-      <c r="AC16" s="20"/>
-      <c r="AD16" s="21"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="47"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="47"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="47"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="47"/>
+      <c r="W16" s="23"/>
+      <c r="X16" s="70"/>
+      <c r="Y16" s="19"/>
+      <c r="Z16" s="19"/>
+      <c r="AA16" s="19"/>
+      <c r="AB16" s="19"/>
+      <c r="AC16" s="19"/>
+      <c r="AD16" s="20"/>
       <c r="AH16" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C15:F15), 1), BIN2HEX(_xlfn.CONCAT(G15:N15), 2), BIN2HEX(_xlfn.CONCAT(O15:V15), 2), BIN2HEX(_xlfn.CONCAT(W15:AD15), 2) )</f>
         <v>188413F</v>
       </c>
     </row>
     <row r="17" spans="1:34" ht="32.15" customHeight="1">
-      <c r="A17" s="49"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="25"/>
-      <c r="S17" s="36"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-      <c r="V17" s="36"/>
-      <c r="W17" s="25"/>
-      <c r="X17" s="72"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="31"/>
-      <c r="AA17" s="31"/>
-      <c r="AB17" s="31"/>
-      <c r="AC17" s="31"/>
-      <c r="AD17" s="22"/>
+      <c r="A17" s="48"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="24"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="24"/>
+      <c r="X17" s="71"/>
+      <c r="Y17" s="30"/>
+      <c r="Z17" s="30"/>
+      <c r="AA17" s="30"/>
+      <c r="AB17" s="30"/>
+      <c r="AC17" s="30"/>
+      <c r="AD17" s="21"/>
     </row>
     <row r="18" spans="1:34">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="69">
-        <v>0</v>
-      </c>
-      <c r="D18" s="69">
-        <v>0</v>
-      </c>
-      <c r="E18" s="69">
-        <v>0</v>
-      </c>
-      <c r="F18" s="69">
-        <v>0</v>
-      </c>
-      <c r="G18" s="69">
-        <v>0</v>
-      </c>
-      <c r="H18" s="69">
-        <v>0</v>
-      </c>
-      <c r="I18" s="25">
-        <v>0</v>
-      </c>
-      <c r="J18" s="25">
-        <v>0</v>
-      </c>
-      <c r="K18" s="25">
-        <v>0</v>
-      </c>
-      <c r="L18" s="25">
-        <v>0</v>
-      </c>
-      <c r="M18" s="25">
-        <v>0</v>
-      </c>
-      <c r="N18" s="36">
-        <v>0</v>
-      </c>
-      <c r="O18" s="25">
-        <v>0</v>
-      </c>
-      <c r="P18" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="36">
-        <v>0</v>
-      </c>
-      <c r="R18" s="25">
-        <v>0</v>
-      </c>
-      <c r="S18" s="36">
-        <v>0</v>
-      </c>
-      <c r="T18" s="25">
-        <v>0</v>
-      </c>
-      <c r="U18" s="25">
-        <v>0</v>
-      </c>
-      <c r="V18" s="36">
-        <v>0</v>
-      </c>
-      <c r="W18" s="25">
-        <v>0</v>
-      </c>
-      <c r="X18" s="72">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD18" s="22">
+      <c r="C18" s="68">
+        <v>0</v>
+      </c>
+      <c r="D18" s="68">
+        <v>0</v>
+      </c>
+      <c r="E18" s="68">
+        <v>0</v>
+      </c>
+      <c r="F18" s="68">
+        <v>0</v>
+      </c>
+      <c r="G18" s="68">
+        <v>0</v>
+      </c>
+      <c r="H18" s="68">
+        <v>0</v>
+      </c>
+      <c r="I18" s="24">
+        <v>0</v>
+      </c>
+      <c r="J18" s="24">
+        <v>0</v>
+      </c>
+      <c r="K18" s="24">
+        <v>0</v>
+      </c>
+      <c r="L18" s="24">
+        <v>0</v>
+      </c>
+      <c r="M18" s="24">
+        <v>0</v>
+      </c>
+      <c r="N18" s="35">
+        <v>0</v>
+      </c>
+      <c r="O18" s="24">
+        <v>0</v>
+      </c>
+      <c r="P18" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="35">
+        <v>0</v>
+      </c>
+      <c r="R18" s="24">
+        <v>0</v>
+      </c>
+      <c r="S18" s="35">
+        <v>0</v>
+      </c>
+      <c r="T18" s="24">
+        <v>0</v>
+      </c>
+      <c r="U18" s="24">
+        <v>0</v>
+      </c>
+      <c r="V18" s="35">
+        <v>0</v>
+      </c>
+      <c r="W18" s="24">
+        <v>0</v>
+      </c>
+      <c r="X18" s="71">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:34">
-      <c r="A19" s="49" t="s">
+      <c r="A19" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="69">
-        <v>0</v>
-      </c>
-      <c r="D19" s="69">
-        <v>0</v>
-      </c>
-      <c r="E19" s="69">
-        <v>0</v>
-      </c>
-      <c r="F19" s="69">
-        <v>0</v>
-      </c>
-      <c r="G19" s="69">
-        <v>0</v>
-      </c>
-      <c r="H19" s="69">
-        <v>1</v>
-      </c>
-      <c r="I19" s="25">
-        <v>0</v>
-      </c>
-      <c r="J19" s="25">
-        <v>0</v>
-      </c>
-      <c r="K19" s="25">
-        <v>0</v>
-      </c>
-      <c r="L19" s="25">
-        <v>0</v>
-      </c>
-      <c r="M19" s="25">
-        <v>0</v>
-      </c>
-      <c r="N19" s="36">
-        <v>1</v>
-      </c>
-      <c r="O19" s="26">
-        <v>0</v>
-      </c>
-      <c r="P19" s="73">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="36">
-        <v>0</v>
-      </c>
-      <c r="R19" s="25">
-        <v>1</v>
-      </c>
-      <c r="S19" s="36">
-        <v>0</v>
-      </c>
-      <c r="T19" s="25">
-        <v>0</v>
-      </c>
-      <c r="U19" s="25">
-        <v>0</v>
-      </c>
-      <c r="V19" s="36">
-        <v>0</v>
-      </c>
-      <c r="W19" s="25">
-        <v>0</v>
-      </c>
-      <c r="X19" s="72">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD19" s="22">
+      <c r="C19" s="68">
+        <v>0</v>
+      </c>
+      <c r="D19" s="68">
+        <v>0</v>
+      </c>
+      <c r="E19" s="68">
+        <v>0</v>
+      </c>
+      <c r="F19" s="68">
+        <v>0</v>
+      </c>
+      <c r="G19" s="68">
+        <v>0</v>
+      </c>
+      <c r="H19" s="68">
+        <v>1</v>
+      </c>
+      <c r="I19" s="24">
+        <v>0</v>
+      </c>
+      <c r="J19" s="24">
+        <v>0</v>
+      </c>
+      <c r="K19" s="24">
+        <v>0</v>
+      </c>
+      <c r="L19" s="24">
+        <v>0</v>
+      </c>
+      <c r="M19" s="24">
+        <v>0</v>
+      </c>
+      <c r="N19" s="35">
+        <v>1</v>
+      </c>
+      <c r="O19" s="25">
+        <v>0</v>
+      </c>
+      <c r="P19" s="72">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="35">
+        <v>0</v>
+      </c>
+      <c r="R19" s="24">
+        <v>1</v>
+      </c>
+      <c r="S19" s="35">
+        <v>0</v>
+      </c>
+      <c r="T19" s="24">
+        <v>0</v>
+      </c>
+      <c r="U19" s="24">
+        <v>0</v>
+      </c>
+      <c r="V19" s="35">
+        <v>0</v>
+      </c>
+      <c r="W19" s="24">
+        <v>0</v>
+      </c>
+      <c r="X19" s="71">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="21">
         <v>1</v>
       </c>
       <c r="AH19" t="str">
@@ -2392,10 +2391,10 @@
       </c>
     </row>
     <row r="20" spans="1:34" ht="30">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="46"/>
+      <c r="B20" s="45"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -2408,8 +2407,8 @@
       <c r="L20" s="12"/>
       <c r="M20" s="14"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="72"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="71"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="14"/>
       <c r="S20" s="9"/>
@@ -2417,20 +2416,20 @@
       <c r="U20" s="14"/>
       <c r="V20" s="9"/>
       <c r="W20" s="17"/>
-      <c r="X20" s="65"/>
-      <c r="Y20" s="20"/>
-      <c r="Z20" s="20"/>
-      <c r="AA20" s="20"/>
-      <c r="AB20" s="20"/>
-      <c r="AC20" s="20"/>
-      <c r="AD20" s="21"/>
+      <c r="X20" s="64"/>
+      <c r="Y20" s="19"/>
+      <c r="Z20" s="19"/>
+      <c r="AA20" s="19"/>
+      <c r="AB20" s="19"/>
+      <c r="AC20" s="19"/>
+      <c r="AD20" s="20"/>
       <c r="AH20" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C19:F19), 1), BIN2HEX(_xlfn.CONCAT(G19:N19), 2), BIN2HEX(_xlfn.CONCAT(O19:V19), 2), BIN2HEX(_xlfn.CONCAT(W19:AD19), 2) )</f>
         <v>041103F</v>
       </c>
     </row>
     <row r="21" spans="1:34" ht="32.15" customHeight="1">
-      <c r="A21" s="49"/>
+      <c r="A21" s="48"/>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
@@ -2442,26 +2441,26 @@
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="25"/>
-      <c r="P21" s="72"/>
-      <c r="Q21" s="30"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="29"/>
       <c r="R21" s="15"/>
-      <c r="S21" s="30"/>
+      <c r="S21" s="29"/>
       <c r="T21" s="15"/>
       <c r="U21" s="15"/>
-      <c r="V21" s="30"/>
+      <c r="V21" s="29"/>
       <c r="W21" s="18"/>
-      <c r="X21" s="66"/>
-      <c r="Y21" s="31"/>
-      <c r="Z21" s="31"/>
-      <c r="AA21" s="31"/>
-      <c r="AB21" s="31"/>
-      <c r="AC21" s="31"/>
-      <c r="AD21" s="22"/>
+      <c r="X21" s="65"/>
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="30"/>
+      <c r="AA21" s="30"/>
+      <c r="AB21" s="30"/>
+      <c r="AC21" s="30"/>
+      <c r="AD21" s="21"/>
     </row>
     <row r="22" spans="1:34">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="48" t="s">
         <v>36</v>
       </c>
       <c r="C22" s="11">
@@ -2497,22 +2496,22 @@
       <c r="M22" s="15">
         <v>0</v>
       </c>
-      <c r="N22" s="30">
-        <v>1</v>
-      </c>
-      <c r="O22" s="26">
-        <v>0</v>
-      </c>
-      <c r="P22" s="73">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="30">
+      <c r="N22" s="29">
+        <v>1</v>
+      </c>
+      <c r="O22" s="25">
+        <v>0</v>
+      </c>
+      <c r="P22" s="72">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="29">
         <v>1</v>
       </c>
       <c r="R22" s="15">
         <v>1</v>
       </c>
-      <c r="S22" s="30">
+      <c r="S22" s="29">
         <v>1</v>
       </c>
       <c r="T22" s="15">
@@ -2521,278 +2520,278 @@
       <c r="U22" s="15">
         <v>0</v>
       </c>
-      <c r="V22" s="30">
+      <c r="V22" s="29">
         <v>0</v>
       </c>
       <c r="W22" s="18">
         <v>0</v>
       </c>
-      <c r="X22" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC22" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD22" s="22">
+      <c r="X22" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD22" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:34" ht="31">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="48"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="48"/>
-      <c r="T23" s="24"/>
-      <c r="U23" s="24"/>
-      <c r="V23" s="48"/>
-      <c r="W23" s="24"/>
-      <c r="X23" s="71"/>
-      <c r="Y23" s="20"/>
-      <c r="Z23" s="20"/>
-      <c r="AA23" s="20"/>
-      <c r="AB23" s="20"/>
-      <c r="AC23" s="20"/>
-      <c r="AD23" s="21"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="47"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="47"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="47"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="47"/>
+      <c r="W23" s="23"/>
+      <c r="X23" s="70"/>
+      <c r="Y23" s="19"/>
+      <c r="Z23" s="19"/>
+      <c r="AA23" s="19"/>
+      <c r="AB23" s="19"/>
+      <c r="AC23" s="19"/>
+      <c r="AD23" s="20"/>
       <c r="AH23" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C22:F22), 1), BIN2HEX(_xlfn.CONCAT(G22:N22), 2), BIN2HEX(_xlfn.CONCAT(O22:V22), 2), BIN2HEX(_xlfn.CONCAT(W22:AD22), 2) )</f>
         <v>041783F</v>
       </c>
     </row>
     <row r="24" spans="1:34" ht="32.15" customHeight="1">
-      <c r="A24" s="49"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
-      <c r="N24" s="36"/>
-      <c r="O24" s="25"/>
-      <c r="P24" s="72"/>
-      <c r="Q24" s="36"/>
-      <c r="R24" s="25"/>
-      <c r="S24" s="36"/>
-      <c r="T24" s="25"/>
-      <c r="U24" s="25"/>
-      <c r="V24" s="36"/>
-      <c r="W24" s="25"/>
-      <c r="X24" s="72"/>
-      <c r="Y24" s="31"/>
-      <c r="Z24" s="31"/>
-      <c r="AA24" s="31"/>
-      <c r="AB24" s="31"/>
-      <c r="AC24" s="31"/>
-      <c r="AD24" s="22"/>
+      <c r="A24" s="48"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="24"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="24"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="24"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="24"/>
+      <c r="U24" s="24"/>
+      <c r="V24" s="35"/>
+      <c r="W24" s="24"/>
+      <c r="X24" s="71"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="30"/>
+      <c r="AA24" s="30"/>
+      <c r="AB24" s="30"/>
+      <c r="AC24" s="30"/>
+      <c r="AD24" s="21"/>
     </row>
     <row r="25" spans="1:34">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="69">
-        <v>0</v>
-      </c>
-      <c r="D25" s="69">
-        <v>0</v>
-      </c>
-      <c r="E25" s="69">
-        <v>0</v>
-      </c>
-      <c r="F25" s="69">
-        <v>0</v>
-      </c>
-      <c r="G25" s="69">
-        <v>0</v>
-      </c>
-      <c r="H25" s="69">
-        <v>0</v>
-      </c>
-      <c r="I25" s="25">
-        <v>0</v>
-      </c>
-      <c r="J25" s="25">
-        <v>0</v>
-      </c>
-      <c r="K25" s="25">
-        <v>0</v>
-      </c>
-      <c r="L25" s="25">
-        <v>0</v>
-      </c>
-      <c r="M25" s="25">
-        <v>0</v>
-      </c>
-      <c r="N25" s="36">
-        <v>0</v>
-      </c>
-      <c r="O25" s="25">
-        <v>0</v>
-      </c>
-      <c r="P25" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="36">
-        <v>0</v>
-      </c>
-      <c r="R25" s="25">
-        <v>0</v>
-      </c>
-      <c r="S25" s="36">
-        <v>0</v>
-      </c>
-      <c r="T25" s="25">
-        <v>0</v>
-      </c>
-      <c r="U25" s="25">
-        <v>0</v>
-      </c>
-      <c r="V25" s="36">
-        <v>0</v>
-      </c>
-      <c r="W25" s="25">
-        <v>0</v>
-      </c>
-      <c r="X25" s="72">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA25" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC25" s="31">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="22">
+      <c r="C25" s="68">
+        <v>0</v>
+      </c>
+      <c r="D25" s="68">
+        <v>0</v>
+      </c>
+      <c r="E25" s="68">
+        <v>0</v>
+      </c>
+      <c r="F25" s="68">
+        <v>0</v>
+      </c>
+      <c r="G25" s="68">
+        <v>0</v>
+      </c>
+      <c r="H25" s="68">
+        <v>0</v>
+      </c>
+      <c r="I25" s="24">
+        <v>0</v>
+      </c>
+      <c r="J25" s="24">
+        <v>0</v>
+      </c>
+      <c r="K25" s="24">
+        <v>0</v>
+      </c>
+      <c r="L25" s="24">
+        <v>0</v>
+      </c>
+      <c r="M25" s="24">
+        <v>0</v>
+      </c>
+      <c r="N25" s="35">
+        <v>0</v>
+      </c>
+      <c r="O25" s="24">
+        <v>0</v>
+      </c>
+      <c r="P25" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="35">
+        <v>0</v>
+      </c>
+      <c r="R25" s="24">
+        <v>0</v>
+      </c>
+      <c r="S25" s="35">
+        <v>0</v>
+      </c>
+      <c r="T25" s="24">
+        <v>0</v>
+      </c>
+      <c r="U25" s="24">
+        <v>0</v>
+      </c>
+      <c r="V25" s="35">
+        <v>0</v>
+      </c>
+      <c r="W25" s="24">
+        <v>0</v>
+      </c>
+      <c r="X25" s="71">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:34">
-      <c r="A26" s="49" t="s">
+      <c r="A26" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="69">
-        <v>0</v>
-      </c>
-      <c r="D26" s="69">
-        <v>0</v>
-      </c>
-      <c r="E26" s="69">
-        <v>0</v>
-      </c>
-      <c r="F26" s="69">
-        <v>1</v>
-      </c>
-      <c r="G26" s="69">
-        <v>0</v>
-      </c>
-      <c r="H26" s="69">
-        <v>1</v>
-      </c>
-      <c r="I26" s="25">
-        <v>1</v>
-      </c>
-      <c r="J26" s="25">
-        <v>0</v>
-      </c>
-      <c r="K26" s="25">
-        <v>0</v>
-      </c>
-      <c r="L26" s="25">
-        <v>0</v>
-      </c>
-      <c r="M26" s="25">
-        <v>0</v>
-      </c>
-      <c r="N26" s="36">
-        <v>1</v>
-      </c>
-      <c r="O26" s="25">
-        <v>1</v>
-      </c>
-      <c r="P26" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="36">
-        <v>0</v>
-      </c>
-      <c r="R26" s="25">
-        <v>1</v>
-      </c>
-      <c r="S26" s="36">
-        <v>1</v>
-      </c>
-      <c r="T26" s="25">
-        <v>0</v>
-      </c>
-      <c r="U26" s="25">
-        <v>0</v>
-      </c>
-      <c r="V26" s="36">
-        <v>0</v>
-      </c>
-      <c r="W26" s="25">
-        <v>0</v>
-      </c>
-      <c r="X26" s="72">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD26" s="22">
+      <c r="C26" s="68">
+        <v>0</v>
+      </c>
+      <c r="D26" s="68">
+        <v>0</v>
+      </c>
+      <c r="E26" s="68">
+        <v>0</v>
+      </c>
+      <c r="F26" s="68">
+        <v>1</v>
+      </c>
+      <c r="G26" s="68">
+        <v>0</v>
+      </c>
+      <c r="H26" s="68">
+        <v>1</v>
+      </c>
+      <c r="I26" s="24">
+        <v>1</v>
+      </c>
+      <c r="J26" s="24">
+        <v>0</v>
+      </c>
+      <c r="K26" s="24">
+        <v>0</v>
+      </c>
+      <c r="L26" s="24">
+        <v>0</v>
+      </c>
+      <c r="M26" s="24">
+        <v>0</v>
+      </c>
+      <c r="N26" s="35">
+        <v>1</v>
+      </c>
+      <c r="O26" s="24">
+        <v>1</v>
+      </c>
+      <c r="P26" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="35">
+        <v>0</v>
+      </c>
+      <c r="R26" s="24">
+        <v>1</v>
+      </c>
+      <c r="S26" s="35">
+        <v>1</v>
+      </c>
+      <c r="T26" s="24">
+        <v>0</v>
+      </c>
+      <c r="U26" s="24">
+        <v>0</v>
+      </c>
+      <c r="V26" s="35">
+        <v>0</v>
+      </c>
+      <c r="W26" s="24">
+        <v>0</v>
+      </c>
+      <c r="X26" s="71">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="21">
         <v>1</v>
       </c>
       <c r="AH26" t="str">
@@ -2801,91 +2800,91 @@
       </c>
     </row>
     <row r="27" spans="1:34">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="69">
-        <v>0</v>
-      </c>
-      <c r="D27" s="69">
-        <v>0</v>
-      </c>
-      <c r="E27" s="69">
-        <v>0</v>
-      </c>
-      <c r="F27" s="69">
-        <v>1</v>
-      </c>
-      <c r="G27" s="69">
-        <v>0</v>
-      </c>
-      <c r="H27" s="69">
-        <v>1</v>
-      </c>
-      <c r="I27" s="25">
-        <v>1</v>
-      </c>
-      <c r="J27" s="25">
-        <v>0</v>
-      </c>
-      <c r="K27" s="25">
-        <v>0</v>
-      </c>
-      <c r="L27" s="25">
-        <v>0</v>
-      </c>
-      <c r="M27" s="25">
-        <v>0</v>
-      </c>
-      <c r="N27" s="36">
-        <v>1</v>
-      </c>
-      <c r="O27" s="26">
-        <v>1</v>
-      </c>
-      <c r="P27" s="73">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="36">
-        <v>1</v>
-      </c>
-      <c r="R27" s="25">
-        <v>0</v>
-      </c>
-      <c r="S27" s="36">
-        <v>0</v>
-      </c>
-      <c r="T27" s="25">
-        <v>0</v>
-      </c>
-      <c r="U27" s="25">
-        <v>0</v>
-      </c>
-      <c r="V27" s="36">
-        <v>0</v>
-      </c>
-      <c r="W27" s="25">
-        <v>0</v>
-      </c>
-      <c r="X27" s="72">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB27" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC27" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD27" s="22">
+      <c r="C27" s="68">
+        <v>0</v>
+      </c>
+      <c r="D27" s="68">
+        <v>0</v>
+      </c>
+      <c r="E27" s="68">
+        <v>0</v>
+      </c>
+      <c r="F27" s="68">
+        <v>1</v>
+      </c>
+      <c r="G27" s="68">
+        <v>0</v>
+      </c>
+      <c r="H27" s="68">
+        <v>1</v>
+      </c>
+      <c r="I27" s="24">
+        <v>1</v>
+      </c>
+      <c r="J27" s="24">
+        <v>0</v>
+      </c>
+      <c r="K27" s="24">
+        <v>0</v>
+      </c>
+      <c r="L27" s="24">
+        <v>0</v>
+      </c>
+      <c r="M27" s="24">
+        <v>0</v>
+      </c>
+      <c r="N27" s="35">
+        <v>1</v>
+      </c>
+      <c r="O27" s="25">
+        <v>1</v>
+      </c>
+      <c r="P27" s="72">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="35">
+        <v>1</v>
+      </c>
+      <c r="R27" s="24">
+        <v>0</v>
+      </c>
+      <c r="S27" s="35">
+        <v>0</v>
+      </c>
+      <c r="T27" s="24">
+        <v>0</v>
+      </c>
+      <c r="U27" s="24">
+        <v>0</v>
+      </c>
+      <c r="V27" s="35">
+        <v>0</v>
+      </c>
+      <c r="W27" s="24">
+        <v>0</v>
+      </c>
+      <c r="X27" s="71">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="21">
         <v>1</v>
       </c>
       <c r="AH27" t="str">
@@ -2894,10 +2893,10 @@
       </c>
     </row>
     <row r="28" spans="1:34" ht="31">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="46"/>
+      <c r="B28" s="45"/>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
@@ -2910,8 +2909,8 @@
       <c r="L28" s="12"/>
       <c r="M28" s="14"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="25"/>
-      <c r="P28" s="72"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="71"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="14"/>
       <c r="S28" s="9"/>
@@ -2919,20 +2918,20 @@
       <c r="U28" s="14"/>
       <c r="V28" s="9"/>
       <c r="W28" s="17"/>
-      <c r="X28" s="65"/>
-      <c r="Y28" s="20"/>
-      <c r="Z28" s="20"/>
-      <c r="AA28" s="20"/>
-      <c r="AB28" s="20"/>
-      <c r="AC28" s="20"/>
-      <c r="AD28" s="21"/>
+      <c r="X28" s="64"/>
+      <c r="Y28" s="19"/>
+      <c r="Z28" s="19"/>
+      <c r="AA28" s="19"/>
+      <c r="AB28" s="19"/>
+      <c r="AC28" s="19"/>
+      <c r="AD28" s="20"/>
       <c r="AH28" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C27:F27), 1), BIN2HEX(_xlfn.CONCAT(G27:N27), 2), BIN2HEX(_xlfn.CONCAT(O27:V27), 2), BIN2HEX(_xlfn.CONCAT(W27:AD27), 2) )</f>
         <v>161E03F</v>
       </c>
     </row>
     <row r="29" spans="1:34" ht="32.15" customHeight="1">
-      <c r="A29" s="49"/>
+      <c r="A29" s="48"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
@@ -2944,26 +2943,26 @@
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
       <c r="M29" s="15"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="25"/>
-      <c r="P29" s="72"/>
-      <c r="Q29" s="30"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="24"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="29"/>
       <c r="R29" s="15"/>
-      <c r="S29" s="30"/>
+      <c r="S29" s="29"/>
       <c r="T29" s="15"/>
       <c r="U29" s="15"/>
-      <c r="V29" s="30"/>
+      <c r="V29" s="29"/>
       <c r="W29" s="18"/>
-      <c r="X29" s="66"/>
-      <c r="Y29" s="31"/>
-      <c r="Z29" s="31"/>
-      <c r="AA29" s="31"/>
-      <c r="AB29" s="31"/>
-      <c r="AC29" s="31"/>
-      <c r="AD29" s="22"/>
+      <c r="X29" s="65"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="21"/>
     </row>
     <row r="30" spans="1:34">
-      <c r="A30" s="49" t="s">
+      <c r="A30" s="48" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="11">
@@ -2999,22 +2998,22 @@
       <c r="M30" s="15">
         <v>0</v>
       </c>
-      <c r="N30" s="30">
-        <v>0</v>
-      </c>
-      <c r="O30" s="25">
-        <v>0</v>
-      </c>
-      <c r="P30" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="30">
+      <c r="N30" s="29">
+        <v>0</v>
+      </c>
+      <c r="O30" s="24">
+        <v>0</v>
+      </c>
+      <c r="P30" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="29">
         <v>0</v>
       </c>
       <c r="R30" s="15">
         <v>1</v>
       </c>
-      <c r="S30" s="30">
+      <c r="S30" s="29">
         <v>0</v>
       </c>
       <c r="T30" s="15">
@@ -3023,36 +3022,36 @@
       <c r="U30" s="15">
         <v>0</v>
       </c>
-      <c r="V30" s="30">
+      <c r="V30" s="29">
         <v>0</v>
       </c>
       <c r="W30" s="18">
         <v>0</v>
       </c>
-      <c r="X30" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA30" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD30" s="22">
+      <c r="X30" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD30" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:34">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="48" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="11">
@@ -3088,22 +3087,22 @@
       <c r="M31" s="15">
         <v>0</v>
       </c>
-      <c r="N31" s="30">
-        <v>0</v>
-      </c>
-      <c r="O31" s="25">
-        <v>0</v>
-      </c>
-      <c r="P31" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="30">
+      <c r="N31" s="29">
+        <v>0</v>
+      </c>
+      <c r="O31" s="24">
+        <v>0</v>
+      </c>
+      <c r="P31" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="29">
         <v>0</v>
       </c>
       <c r="R31" s="15">
         <v>0</v>
       </c>
-      <c r="S31" s="30">
+      <c r="S31" s="29">
         <v>0</v>
       </c>
       <c r="T31" s="15">
@@ -3112,31 +3111,31 @@
       <c r="U31" s="15">
         <v>0</v>
       </c>
-      <c r="V31" s="30">
+      <c r="V31" s="29">
         <v>0</v>
       </c>
       <c r="W31" s="18">
         <v>1</v>
       </c>
-      <c r="X31" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD31" s="22">
+      <c r="X31" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD31" s="21">
         <v>0</v>
       </c>
       <c r="AH31" t="str">
@@ -3145,7 +3144,7 @@
       </c>
     </row>
     <row r="32" spans="1:34">
-      <c r="A32" s="49" t="s">
+      <c r="A32" s="48" t="s">
         <v>44</v>
       </c>
       <c r="C32" s="11">
@@ -3181,22 +3180,22 @@
       <c r="M32" s="15">
         <v>0</v>
       </c>
-      <c r="N32" s="30">
-        <v>0</v>
-      </c>
-      <c r="O32" s="26">
-        <v>0</v>
-      </c>
-      <c r="P32" s="73">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="30">
+      <c r="N32" s="29">
+        <v>0</v>
+      </c>
+      <c r="O32" s="25">
+        <v>0</v>
+      </c>
+      <c r="P32" s="72">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="29">
         <v>0</v>
       </c>
       <c r="R32" s="15">
         <v>0</v>
       </c>
-      <c r="S32" s="30">
+      <c r="S32" s="29">
         <v>0</v>
       </c>
       <c r="T32" s="15">
@@ -3205,31 +3204,31 @@
       <c r="U32" s="15">
         <v>0</v>
       </c>
-      <c r="V32" s="30">
+      <c r="V32" s="29">
         <v>0</v>
       </c>
       <c r="W32" s="18">
         <v>0</v>
       </c>
-      <c r="X32" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA32" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB32" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD32" s="22">
+      <c r="X32" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD32" s="21">
         <v>1</v>
       </c>
       <c r="AH32" t="str">
@@ -3238,10 +3237,10 @@
       </c>
     </row>
     <row r="33" spans="1:34" ht="31">
-      <c r="A33" s="45" t="s">
+      <c r="A33" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="46"/>
+      <c r="B33" s="45"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
@@ -3254,8 +3253,8 @@
       <c r="L33" s="12"/>
       <c r="M33" s="14"/>
       <c r="N33" s="9"/>
-      <c r="O33" s="25"/>
-      <c r="P33" s="72"/>
+      <c r="O33" s="24"/>
+      <c r="P33" s="71"/>
       <c r="Q33" s="9"/>
       <c r="R33" s="14"/>
       <c r="S33" s="9"/>
@@ -3263,20 +3262,20 @@
       <c r="U33" s="14"/>
       <c r="V33" s="9"/>
       <c r="W33" s="17"/>
-      <c r="X33" s="65"/>
-      <c r="Y33" s="20"/>
-      <c r="Z33" s="20"/>
-      <c r="AA33" s="20"/>
-      <c r="AB33" s="20"/>
-      <c r="AC33" s="20"/>
-      <c r="AD33" s="21"/>
+      <c r="X33" s="64"/>
+      <c r="Y33" s="19"/>
+      <c r="Z33" s="19"/>
+      <c r="AA33" s="19"/>
+      <c r="AB33" s="19"/>
+      <c r="AC33" s="19"/>
+      <c r="AD33" s="20"/>
       <c r="AH33" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C32:F32), 1), BIN2HEX(_xlfn.CONCAT(G32:N32), 2), BIN2HEX(_xlfn.CONCAT(O32:V32), 2), BIN2HEX(_xlfn.CONCAT(W32:AD32), 2) )</f>
         <v>190003F</v>
       </c>
     </row>
     <row r="34" spans="1:34" ht="32.15" customHeight="1">
-      <c r="A34" s="49"/>
+      <c r="A34" s="48"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
@@ -3288,26 +3287,26 @@
       <c r="K34" s="13"/>
       <c r="L34" s="13"/>
       <c r="M34" s="15"/>
-      <c r="N34" s="30"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="72"/>
-      <c r="Q34" s="30"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="29"/>
       <c r="R34" s="15"/>
-      <c r="S34" s="30"/>
+      <c r="S34" s="29"/>
       <c r="T34" s="15"/>
       <c r="U34" s="15"/>
-      <c r="V34" s="30"/>
+      <c r="V34" s="29"/>
       <c r="W34" s="18"/>
-      <c r="X34" s="66"/>
-      <c r="Y34" s="31"/>
-      <c r="Z34" s="31"/>
-      <c r="AA34" s="31"/>
-      <c r="AB34" s="31"/>
-      <c r="AC34" s="31"/>
-      <c r="AD34" s="22"/>
+      <c r="X34" s="65"/>
+      <c r="Y34" s="30"/>
+      <c r="Z34" s="30"/>
+      <c r="AA34" s="30"/>
+      <c r="AB34" s="30"/>
+      <c r="AC34" s="30"/>
+      <c r="AD34" s="21"/>
     </row>
     <row r="35" spans="1:34">
-      <c r="A35" s="49" t="s">
+      <c r="A35" s="48" t="s">
         <v>46</v>
       </c>
       <c r="C35" s="11">
@@ -3343,22 +3342,22 @@
       <c r="M35" s="15">
         <v>0</v>
       </c>
-      <c r="N35" s="30">
-        <v>0</v>
-      </c>
-      <c r="O35" s="25">
-        <v>0</v>
-      </c>
-      <c r="P35" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="30">
+      <c r="N35" s="29">
+        <v>0</v>
+      </c>
+      <c r="O35" s="24">
+        <v>0</v>
+      </c>
+      <c r="P35" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="29">
         <v>0</v>
       </c>
       <c r="R35" s="15">
         <v>1</v>
       </c>
-      <c r="S35" s="30">
+      <c r="S35" s="29">
         <v>0</v>
       </c>
       <c r="T35" s="15">
@@ -3367,36 +3366,36 @@
       <c r="U35" s="15">
         <v>0</v>
       </c>
-      <c r="V35" s="30">
+      <c r="V35" s="29">
         <v>0</v>
       </c>
       <c r="W35" s="18">
         <v>0</v>
       </c>
-      <c r="X35" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA35" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD35" s="22">
+      <c r="X35" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD35" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:34">
-      <c r="A36" s="49" t="s">
+      <c r="A36" s="48" t="s">
         <v>47</v>
       </c>
       <c r="C36" s="11">
@@ -3432,22 +3431,22 @@
       <c r="M36" s="15">
         <v>0</v>
       </c>
-      <c r="N36" s="30">
-        <v>0</v>
-      </c>
-      <c r="O36" s="25">
-        <v>0</v>
-      </c>
-      <c r="P36" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="30">
+      <c r="N36" s="29">
+        <v>0</v>
+      </c>
+      <c r="O36" s="24">
+        <v>0</v>
+      </c>
+      <c r="P36" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="29">
         <v>0</v>
       </c>
       <c r="R36" s="15">
         <v>0</v>
       </c>
-      <c r="S36" s="30">
+      <c r="S36" s="29">
         <v>0</v>
       </c>
       <c r="T36" s="15">
@@ -3456,31 +3455,31 @@
       <c r="U36" s="15">
         <v>0</v>
       </c>
-      <c r="V36" s="30">
+      <c r="V36" s="29">
         <v>0</v>
       </c>
       <c r="W36" s="18">
         <v>1</v>
       </c>
-      <c r="X36" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z36" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD36" s="22">
+      <c r="X36" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD36" s="21">
         <v>0</v>
       </c>
       <c r="AH36" t="str">
@@ -3489,7 +3488,7 @@
       </c>
     </row>
     <row r="37" spans="1:34">
-      <c r="A37" s="49" t="s">
+      <c r="A37" s="48" t="s">
         <v>48</v>
       </c>
       <c r="C37" s="11">
@@ -3525,22 +3524,22 @@
       <c r="M37" s="15">
         <v>0</v>
       </c>
-      <c r="N37" s="30">
-        <v>0</v>
-      </c>
-      <c r="O37" s="25">
-        <v>0</v>
-      </c>
-      <c r="P37" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="30">
+      <c r="N37" s="29">
+        <v>0</v>
+      </c>
+      <c r="O37" s="24">
+        <v>0</v>
+      </c>
+      <c r="P37" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="29">
         <v>0</v>
       </c>
       <c r="R37" s="15">
         <v>0</v>
       </c>
-      <c r="S37" s="30">
+      <c r="S37" s="29">
         <v>0</v>
       </c>
       <c r="T37" s="15">
@@ -3549,31 +3548,31 @@
       <c r="U37" s="15">
         <v>0</v>
       </c>
-      <c r="V37" s="30">
+      <c r="V37" s="29">
         <v>0</v>
       </c>
       <c r="W37" s="18">
         <v>0</v>
       </c>
-      <c r="X37" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA37" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD37" s="22">
+      <c r="X37" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD37" s="21">
         <v>0</v>
       </c>
       <c r="AH37" t="str">
@@ -3582,7 +3581,7 @@
       </c>
     </row>
     <row r="38" spans="1:34">
-      <c r="A38" s="49" t="s">
+      <c r="A38" s="48" t="s">
         <v>49</v>
       </c>
       <c r="C38" s="11">
@@ -3618,22 +3617,22 @@
       <c r="M38" s="15">
         <v>0</v>
       </c>
-      <c r="N38" s="30">
-        <v>0</v>
-      </c>
-      <c r="O38" s="25">
-        <v>0</v>
-      </c>
-      <c r="P38" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="30">
+      <c r="N38" s="29">
+        <v>0</v>
+      </c>
+      <c r="O38" s="24">
+        <v>0</v>
+      </c>
+      <c r="P38" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="29">
         <v>0</v>
       </c>
       <c r="R38" s="15">
         <v>0</v>
       </c>
-      <c r="S38" s="30">
+      <c r="S38" s="29">
         <v>0</v>
       </c>
       <c r="T38" s="15">
@@ -3642,31 +3641,31 @@
       <c r="U38" s="15">
         <v>0</v>
       </c>
-      <c r="V38" s="30">
+      <c r="V38" s="29">
         <v>0</v>
       </c>
       <c r="W38" s="18">
         <v>1</v>
       </c>
-      <c r="X38" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA38" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB38" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC38" s="31">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="22">
+      <c r="X38" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="21">
         <v>1</v>
       </c>
       <c r="AH38" t="str">
@@ -3675,7 +3674,7 @@
       </c>
     </row>
     <row r="39" spans="1:34">
-      <c r="A39" s="49" t="s">
+      <c r="A39" s="48" t="s">
         <v>50</v>
       </c>
       <c r="C39" s="11">
@@ -3711,22 +3710,22 @@
       <c r="M39" s="15">
         <v>0</v>
       </c>
-      <c r="N39" s="30">
-        <v>0</v>
-      </c>
-      <c r="O39" s="26">
-        <v>0</v>
-      </c>
-      <c r="P39" s="73">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="30">
+      <c r="N39" s="29">
+        <v>0</v>
+      </c>
+      <c r="O39" s="25">
+        <v>0</v>
+      </c>
+      <c r="P39" s="72">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="29">
         <v>0</v>
       </c>
       <c r="R39" s="15">
         <v>0</v>
       </c>
-      <c r="S39" s="30">
+      <c r="S39" s="29">
         <v>0</v>
       </c>
       <c r="T39" s="15">
@@ -3735,31 +3734,31 @@
       <c r="U39" s="15">
         <v>0</v>
       </c>
-      <c r="V39" s="30">
+      <c r="V39" s="29">
         <v>0</v>
       </c>
       <c r="W39" s="18">
         <v>0</v>
       </c>
-      <c r="X39" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z39" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA39" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB39" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD39" s="22">
+      <c r="X39" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD39" s="21">
         <v>1</v>
       </c>
       <c r="AH39" t="str">
@@ -3768,10 +3767,10 @@
       </c>
     </row>
     <row r="40" spans="1:34" ht="31">
-      <c r="A40" s="45" t="s">
+      <c r="A40" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="46"/>
+      <c r="B40" s="45"/>
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
@@ -3784,8 +3783,8 @@
       <c r="L40" s="12"/>
       <c r="M40" s="14"/>
       <c r="N40" s="9"/>
-      <c r="O40" s="72"/>
-      <c r="P40" s="36"/>
+      <c r="O40" s="71"/>
+      <c r="P40" s="35"/>
       <c r="Q40" s="9"/>
       <c r="R40" s="14"/>
       <c r="S40" s="9"/>
@@ -3793,20 +3792,20 @@
       <c r="U40" s="14"/>
       <c r="V40" s="9"/>
       <c r="W40" s="17"/>
-      <c r="X40" s="65"/>
-      <c r="Y40" s="20"/>
-      <c r="Z40" s="20"/>
-      <c r="AA40" s="20"/>
-      <c r="AB40" s="20"/>
-      <c r="AC40" s="20"/>
-      <c r="AD40" s="21"/>
+      <c r="X40" s="64"/>
+      <c r="Y40" s="19"/>
+      <c r="Z40" s="19"/>
+      <c r="AA40" s="19"/>
+      <c r="AB40" s="19"/>
+      <c r="AC40" s="19"/>
+      <c r="AD40" s="20"/>
       <c r="AH40" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C39:F39), 1), BIN2HEX(_xlfn.CONCAT(G39:N39), 2), BIN2HEX(_xlfn.CONCAT(O39:V39), 2), BIN2HEX(_xlfn.CONCAT(W39:AD39), 2) )</f>
         <v>190003F</v>
       </c>
     </row>
     <row r="41" spans="1:34" ht="32.15" customHeight="1">
-      <c r="A41" s="49"/>
+      <c r="A41" s="48"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
@@ -3818,26 +3817,26 @@
       <c r="K41" s="13"/>
       <c r="L41" s="13"/>
       <c r="M41" s="15"/>
-      <c r="N41" s="30"/>
-      <c r="O41" s="72"/>
-      <c r="P41" s="36"/>
-      <c r="Q41" s="30"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="71"/>
+      <c r="P41" s="35"/>
+      <c r="Q41" s="29"/>
       <c r="R41" s="15"/>
-      <c r="S41" s="30"/>
+      <c r="S41" s="29"/>
       <c r="T41" s="15"/>
       <c r="U41" s="15"/>
-      <c r="V41" s="30"/>
+      <c r="V41" s="29"/>
       <c r="W41" s="18"/>
-      <c r="X41" s="66"/>
-      <c r="Y41" s="31"/>
-      <c r="Z41" s="31"/>
-      <c r="AA41" s="31"/>
-      <c r="AB41" s="31"/>
-      <c r="AC41" s="31"/>
-      <c r="AD41" s="22"/>
+      <c r="X41" s="65"/>
+      <c r="Y41" s="30"/>
+      <c r="Z41" s="30"/>
+      <c r="AA41" s="30"/>
+      <c r="AB41" s="30"/>
+      <c r="AC41" s="30"/>
+      <c r="AD41" s="21"/>
     </row>
     <row r="42" spans="1:34">
-      <c r="A42" s="49" t="s">
+      <c r="A42" s="48" t="s">
         <v>52</v>
       </c>
       <c r="C42" s="11">
@@ -3873,22 +3872,22 @@
       <c r="M42" s="15">
         <v>0</v>
       </c>
-      <c r="N42" s="30">
-        <v>0</v>
-      </c>
-      <c r="O42" s="72">
-        <v>0</v>
-      </c>
-      <c r="P42" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q42" s="30">
+      <c r="N42" s="29">
+        <v>0</v>
+      </c>
+      <c r="O42" s="71">
+        <v>0</v>
+      </c>
+      <c r="P42" s="35">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="29">
         <v>1</v>
       </c>
       <c r="R42" s="15">
         <v>0</v>
       </c>
-      <c r="S42" s="30">
+      <c r="S42" s="29">
         <v>1</v>
       </c>
       <c r="T42" s="15">
@@ -3897,36 +3896,36 @@
       <c r="U42" s="15">
         <v>0</v>
       </c>
-      <c r="V42" s="30">
+      <c r="V42" s="29">
         <v>0</v>
       </c>
       <c r="W42" s="18">
         <v>0</v>
       </c>
-      <c r="X42" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA42" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC42" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD42" s="22">
+      <c r="X42" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC42" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD42" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:34">
-      <c r="A43" s="49" t="s">
+      <c r="A43" s="48" t="s">
         <v>53</v>
       </c>
       <c r="C43" s="11">
@@ -3962,22 +3961,22 @@
       <c r="M43" s="15">
         <v>0</v>
       </c>
-      <c r="N43" s="30">
-        <v>0</v>
-      </c>
-      <c r="O43" s="72">
-        <v>0</v>
-      </c>
-      <c r="P43" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="30">
+      <c r="N43" s="29">
+        <v>0</v>
+      </c>
+      <c r="O43" s="71">
+        <v>0</v>
+      </c>
+      <c r="P43" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="29">
         <v>0</v>
       </c>
       <c r="R43" s="15">
         <v>0</v>
       </c>
-      <c r="S43" s="30">
+      <c r="S43" s="29">
         <v>0</v>
       </c>
       <c r="T43" s="15">
@@ -3986,31 +3985,31 @@
       <c r="U43" s="15">
         <v>0</v>
       </c>
-      <c r="V43" s="30">
+      <c r="V43" s="29">
         <v>0</v>
       </c>
       <c r="W43" s="18">
         <v>1</v>
       </c>
-      <c r="X43" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z43" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC43" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD43" s="22">
+      <c r="X43" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z43" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC43" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD43" s="21">
         <v>0</v>
       </c>
       <c r="AH43" t="str">
@@ -4019,7 +4018,7 @@
       </c>
     </row>
     <row r="44" spans="1:34">
-      <c r="A44" s="49" t="s">
+      <c r="A44" s="48" t="s">
         <v>54</v>
       </c>
       <c r="C44" s="11">
@@ -4055,22 +4054,22 @@
       <c r="M44" s="15">
         <v>0</v>
       </c>
-      <c r="N44" s="30">
-        <v>0</v>
-      </c>
-      <c r="O44" s="72">
-        <v>0</v>
-      </c>
-      <c r="P44" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="30">
+      <c r="N44" s="29">
+        <v>0</v>
+      </c>
+      <c r="O44" s="71">
+        <v>0</v>
+      </c>
+      <c r="P44" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="29">
         <v>0</v>
       </c>
       <c r="R44" s="15">
         <v>0</v>
       </c>
-      <c r="S44" s="30">
+      <c r="S44" s="29">
         <v>0</v>
       </c>
       <c r="T44" s="15">
@@ -4079,31 +4078,31 @@
       <c r="U44" s="15">
         <v>0</v>
       </c>
-      <c r="V44" s="30">
+      <c r="V44" s="29">
         <v>0</v>
       </c>
       <c r="W44" s="18">
         <v>0</v>
       </c>
-      <c r="X44" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA44" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB44" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC44" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD44" s="22">
+      <c r="X44" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB44" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC44" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD44" s="21">
         <v>1</v>
       </c>
       <c r="AH44" t="str">
@@ -4112,10 +4111,10 @@
       </c>
     </row>
     <row r="45" spans="1:34" ht="31">
-      <c r="A45" s="45" t="s">
+      <c r="A45" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="46"/>
+      <c r="B45" s="45"/>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
@@ -4128,8 +4127,8 @@
       <c r="L45" s="12"/>
       <c r="M45" s="14"/>
       <c r="N45" s="9"/>
-      <c r="O45" s="24"/>
-      <c r="P45" s="71"/>
+      <c r="O45" s="23"/>
+      <c r="P45" s="70"/>
       <c r="Q45" s="9"/>
       <c r="R45" s="14"/>
       <c r="S45" s="9"/>
@@ -4137,20 +4136,20 @@
       <c r="U45" s="14"/>
       <c r="V45" s="9"/>
       <c r="W45" s="17"/>
-      <c r="X45" s="65"/>
-      <c r="Y45" s="20"/>
-      <c r="Z45" s="20"/>
-      <c r="AA45" s="20"/>
-      <c r="AB45" s="20"/>
-      <c r="AC45" s="20"/>
-      <c r="AD45" s="21"/>
+      <c r="X45" s="64"/>
+      <c r="Y45" s="19"/>
+      <c r="Z45" s="19"/>
+      <c r="AA45" s="19"/>
+      <c r="AB45" s="19"/>
+      <c r="AC45" s="19"/>
+      <c r="AD45" s="20"/>
       <c r="AH45" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C44:F44), 1), BIN2HEX(_xlfn.CONCAT(G44:N44), 2), BIN2HEX(_xlfn.CONCAT(O44:V44), 2), BIN2HEX(_xlfn.CONCAT(W44:AD44), 2) )</f>
         <v>190003F</v>
       </c>
     </row>
     <row r="46" spans="1:34" ht="32.15" customHeight="1">
-      <c r="A46" s="49"/>
+      <c r="A46" s="48"/>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
@@ -4162,26 +4161,26 @@
       <c r="K46" s="13"/>
       <c r="L46" s="13"/>
       <c r="M46" s="15"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="25"/>
-      <c r="P46" s="72"/>
-      <c r="Q46" s="30"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="29"/>
       <c r="R46" s="15"/>
-      <c r="S46" s="30"/>
+      <c r="S46" s="29"/>
       <c r="T46" s="15"/>
       <c r="U46" s="15"/>
-      <c r="V46" s="30"/>
+      <c r="V46" s="29"/>
       <c r="W46" s="18"/>
-      <c r="X46" s="66"/>
-      <c r="Y46" s="31"/>
-      <c r="Z46" s="31"/>
-      <c r="AA46" s="31"/>
-      <c r="AB46" s="31"/>
-      <c r="AC46" s="31"/>
-      <c r="AD46" s="22"/>
+      <c r="X46" s="65"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
+      <c r="AA46" s="30"/>
+      <c r="AB46" s="30"/>
+      <c r="AC46" s="30"/>
+      <c r="AD46" s="21"/>
     </row>
     <row r="47" spans="1:34">
-      <c r="A47" s="49" t="s">
+      <c r="A47" s="48" t="s">
         <v>56</v>
       </c>
       <c r="C47" s="11">
@@ -4220,19 +4219,19 @@
       <c r="N47" s="7">
         <v>0</v>
       </c>
-      <c r="O47" s="25">
-        <v>0</v>
-      </c>
-      <c r="P47" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="30">
+      <c r="O47" s="24">
+        <v>0</v>
+      </c>
+      <c r="P47" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="29">
         <v>0</v>
       </c>
       <c r="R47" s="15">
         <v>0</v>
       </c>
-      <c r="S47" s="30">
+      <c r="S47" s="29">
         <v>1</v>
       </c>
       <c r="T47" s="15">
@@ -4241,39 +4240,39 @@
       <c r="U47" s="15">
         <v>0</v>
       </c>
-      <c r="V47" s="30">
+      <c r="V47" s="29">
         <v>0</v>
       </c>
       <c r="W47" s="18">
         <v>0</v>
       </c>
-      <c r="X47" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z47" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA47" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB47" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC47" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD47" s="22">
+      <c r="X47" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z47" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA47" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB47" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC47" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD47" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:34" ht="31">
-      <c r="A48" s="45" t="s">
+      <c r="A48" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="B48" s="46"/>
+      <c r="B48" s="45"/>
       <c r="C48" s="10"/>
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
@@ -4283,11 +4282,11 @@
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
       <c r="K48" s="12"/>
-      <c r="L48" s="61"/>
-      <c r="M48" s="30"/>
-      <c r="N48" s="30"/>
-      <c r="O48" s="24"/>
-      <c r="P48" s="71"/>
+      <c r="L48" s="60"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="23"/>
+      <c r="P48" s="70"/>
       <c r="Q48" s="9"/>
       <c r="R48" s="14"/>
       <c r="S48" s="9"/>
@@ -4295,20 +4294,20 @@
       <c r="U48" s="14"/>
       <c r="V48" s="9"/>
       <c r="W48" s="17"/>
-      <c r="X48" s="65"/>
-      <c r="Y48" s="20"/>
-      <c r="Z48" s="20"/>
-      <c r="AA48" s="20"/>
-      <c r="AB48" s="20"/>
-      <c r="AC48" s="20"/>
-      <c r="AD48" s="21"/>
+      <c r="X48" s="64"/>
+      <c r="Y48" s="19"/>
+      <c r="Z48" s="19"/>
+      <c r="AA48" s="19"/>
+      <c r="AB48" s="19"/>
+      <c r="AC48" s="19"/>
+      <c r="AD48" s="20"/>
       <c r="AH48" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C47:G47), 1), BIN2HEX(_xlfn.CONCAT(G47:N47), 2), BIN2HEX(_xlfn.CONCAT(O47:V47), 2), BIN2HEX(_xlfn.CONCAT(W47:AD47), 2) )</f>
         <v>3840C3F</v>
       </c>
     </row>
     <row r="49" spans="1:34" ht="32.15" customHeight="1">
-      <c r="A49" s="49"/>
+      <c r="A49" s="48"/>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
       <c r="E49" s="11"/>
@@ -4318,28 +4317,28 @@
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
       <c r="K49" s="13"/>
-      <c r="L49" s="62"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30"/>
-      <c r="O49" s="25"/>
-      <c r="P49" s="72"/>
-      <c r="Q49" s="30"/>
+      <c r="L49" s="61"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="24"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="29"/>
       <c r="R49" s="15"/>
-      <c r="S49" s="30"/>
+      <c r="S49" s="29"/>
       <c r="T49" s="15"/>
       <c r="U49" s="15"/>
-      <c r="V49" s="30"/>
+      <c r="V49" s="29"/>
       <c r="W49" s="18"/>
-      <c r="X49" s="66"/>
-      <c r="Y49" s="31"/>
-      <c r="Z49" s="31"/>
-      <c r="AA49" s="31"/>
-      <c r="AB49" s="31"/>
-      <c r="AC49" s="31"/>
-      <c r="AD49" s="22"/>
+      <c r="X49" s="65"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
+      <c r="AA49" s="30"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="30"/>
+      <c r="AD49" s="21"/>
     </row>
     <row r="50" spans="1:34">
-      <c r="A50" s="49" t="s">
+      <c r="A50" s="48" t="s">
         <v>58</v>
       </c>
       <c r="C50" s="11">
@@ -4369,28 +4368,28 @@
       <c r="K50" s="13">
         <v>1</v>
       </c>
-      <c r="L50" s="62">
-        <v>0</v>
-      </c>
-      <c r="M50" s="30">
-        <v>0</v>
-      </c>
-      <c r="N50" s="30">
-        <v>0</v>
-      </c>
-      <c r="O50" s="25">
-        <v>0</v>
-      </c>
-      <c r="P50" s="72">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="30">
+      <c r="L50" s="61">
+        <v>0</v>
+      </c>
+      <c r="M50" s="29">
+        <v>0</v>
+      </c>
+      <c r="N50" s="29">
+        <v>0</v>
+      </c>
+      <c r="O50" s="24">
+        <v>0</v>
+      </c>
+      <c r="P50" s="71">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="29">
         <v>0</v>
       </c>
       <c r="R50" s="15">
         <v>0</v>
       </c>
-      <c r="S50" s="30">
+      <c r="S50" s="29">
         <v>0</v>
       </c>
       <c r="T50" s="15">
@@ -4399,39 +4398,39 @@
       <c r="U50" s="15">
         <v>1</v>
       </c>
-      <c r="V50" s="30">
+      <c r="V50" s="29">
         <v>0</v>
       </c>
       <c r="W50" s="18">
         <v>0</v>
       </c>
-      <c r="X50" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA50" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB50" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC50" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD50" s="22">
+      <c r="X50" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA50" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB50" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC50" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD50" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:34" ht="31">
-      <c r="A51" s="52" t="s">
+      <c r="A51" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="46"/>
+      <c r="B51" s="45"/>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
       <c r="E51" s="10"/>
@@ -4444,8 +4443,8 @@
       <c r="L51" s="12"/>
       <c r="M51" s="14"/>
       <c r="N51" s="9"/>
-      <c r="O51" s="24"/>
-      <c r="P51" s="71"/>
+      <c r="O51" s="23"/>
+      <c r="P51" s="70"/>
       <c r="Q51" s="9"/>
       <c r="R51" s="14"/>
       <c r="S51" s="9"/>
@@ -4453,20 +4452,20 @@
       <c r="U51" s="14"/>
       <c r="V51" s="9"/>
       <c r="W51" s="17"/>
-      <c r="X51" s="65"/>
-      <c r="Y51" s="20"/>
-      <c r="Z51" s="20"/>
-      <c r="AA51" s="20"/>
-      <c r="AB51" s="20"/>
-      <c r="AC51" s="20"/>
-      <c r="AD51" s="21"/>
+      <c r="X51" s="64"/>
+      <c r="Y51" s="19"/>
+      <c r="Z51" s="19"/>
+      <c r="AA51" s="19"/>
+      <c r="AB51" s="19"/>
+      <c r="AC51" s="19"/>
+      <c r="AD51" s="20"/>
       <c r="AH51" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C50:F50), 1), BIN2HEX(_xlfn.CONCAT(G50:N50), 2), BIN2HEX(_xlfn.CONCAT(O50:V50), 2), BIN2HEX(_xlfn.CONCAT(W50:AD50), 2) )</f>
         <v>188423F</v>
       </c>
     </row>
     <row r="52" spans="1:34" ht="32.15" customHeight="1">
-      <c r="A52" s="49"/>
+      <c r="A52" s="48"/>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
       <c r="E52" s="11"/>
@@ -4478,26 +4477,26 @@
       <c r="K52" s="13"/>
       <c r="L52" s="13"/>
       <c r="M52" s="15"/>
-      <c r="N52" s="30"/>
-      <c r="O52" s="25"/>
-      <c r="P52" s="72"/>
-      <c r="Q52" s="30"/>
+      <c r="N52" s="29"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="29"/>
       <c r="R52" s="15"/>
-      <c r="S52" s="30"/>
+      <c r="S52" s="29"/>
       <c r="T52" s="15"/>
       <c r="U52" s="15"/>
-      <c r="V52" s="30"/>
+      <c r="V52" s="29"/>
       <c r="W52" s="18"/>
-      <c r="X52" s="66"/>
-      <c r="Y52" s="31"/>
-      <c r="Z52" s="31"/>
-      <c r="AA52" s="31"/>
-      <c r="AB52" s="31"/>
-      <c r="AC52" s="31"/>
-      <c r="AD52" s="22"/>
+      <c r="X52" s="65"/>
+      <c r="Y52" s="30"/>
+      <c r="Z52" s="30"/>
+      <c r="AA52" s="30"/>
+      <c r="AB52" s="30"/>
+      <c r="AC52" s="30"/>
+      <c r="AD52" s="21"/>
     </row>
     <row r="53" spans="1:34">
-      <c r="A53" s="49" t="s">
+      <c r="A53" s="48" t="s">
         <v>60</v>
       </c>
       <c r="C53" s="11">
@@ -4533,22 +4532,22 @@
       <c r="M53" s="15">
         <v>0</v>
       </c>
-      <c r="N53" s="30">
-        <v>0</v>
-      </c>
-      <c r="O53" s="25">
-        <v>0</v>
-      </c>
-      <c r="P53" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="30">
+      <c r="N53" s="29">
+        <v>0</v>
+      </c>
+      <c r="O53" s="24">
+        <v>0</v>
+      </c>
+      <c r="P53" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="29">
         <v>0</v>
       </c>
       <c r="R53" s="15">
         <v>1</v>
       </c>
-      <c r="S53" s="30">
+      <c r="S53" s="29">
         <v>0</v>
       </c>
       <c r="T53" s="15">
@@ -4557,36 +4556,36 @@
       <c r="U53" s="15">
         <v>0</v>
       </c>
-      <c r="V53" s="30">
+      <c r="V53" s="29">
         <v>0</v>
       </c>
       <c r="W53" s="18">
         <v>0</v>
       </c>
-      <c r="X53" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA53" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC53" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD53" s="22">
+      <c r="X53" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA53" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD53" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:34">
-      <c r="A54" s="49" t="s">
+      <c r="A54" s="48" t="s">
         <v>61</v>
       </c>
       <c r="C54" s="11">
@@ -4622,22 +4621,22 @@
       <c r="M54" s="15">
         <v>0</v>
       </c>
-      <c r="N54" s="30">
-        <v>0</v>
-      </c>
-      <c r="O54" s="25">
-        <v>0</v>
-      </c>
-      <c r="P54" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="30">
+      <c r="N54" s="29">
+        <v>0</v>
+      </c>
+      <c r="O54" s="24">
+        <v>0</v>
+      </c>
+      <c r="P54" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="29">
         <v>0</v>
       </c>
       <c r="R54" s="15">
         <v>0</v>
       </c>
-      <c r="S54" s="30">
+      <c r="S54" s="29">
         <v>0</v>
       </c>
       <c r="T54" s="15">
@@ -4646,31 +4645,31 @@
       <c r="U54" s="15">
         <v>1</v>
       </c>
-      <c r="V54" s="30">
+      <c r="V54" s="29">
         <v>1</v>
       </c>
       <c r="W54" s="18">
         <v>0</v>
       </c>
-      <c r="X54" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z54" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA54" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB54" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC54" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD54" s="22">
+      <c r="X54" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z54" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD54" s="21">
         <v>1</v>
       </c>
       <c r="AH54" t="str">
@@ -4679,7 +4678,7 @@
       </c>
     </row>
     <row r="55" spans="1:34">
-      <c r="A55" s="49" t="s">
+      <c r="A55" s="48" t="s">
         <v>62</v>
       </c>
       <c r="C55" s="11">
@@ -4715,22 +4714,22 @@
       <c r="M55" s="15">
         <v>0</v>
       </c>
-      <c r="N55" s="30">
-        <v>0</v>
-      </c>
-      <c r="O55" s="25">
-        <v>0</v>
-      </c>
-      <c r="P55" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="30">
+      <c r="N55" s="29">
+        <v>0</v>
+      </c>
+      <c r="O55" s="24">
+        <v>0</v>
+      </c>
+      <c r="P55" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="29">
         <v>0</v>
       </c>
       <c r="R55" s="15">
         <v>0</v>
       </c>
-      <c r="S55" s="30">
+      <c r="S55" s="29">
         <v>0</v>
       </c>
       <c r="T55" s="15">
@@ -4739,31 +4738,31 @@
       <c r="U55" s="15">
         <v>0</v>
       </c>
-      <c r="V55" s="30">
+      <c r="V55" s="29">
         <v>0</v>
       </c>
       <c r="W55" s="18">
         <v>1</v>
       </c>
-      <c r="X55" s="66">
-        <v>1</v>
-      </c>
-      <c r="Y55" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z55" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA55" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB55" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC55" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD55" s="22">
+      <c r="X55" s="65">
+        <v>1</v>
+      </c>
+      <c r="Y55" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z55" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA55" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB55" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC55" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD55" s="21">
         <v>1</v>
       </c>
       <c r="AH55" t="str">
@@ -4772,10 +4771,10 @@
       </c>
     </row>
     <row r="56" spans="1:34" ht="31">
-      <c r="A56" s="52" t="s">
+      <c r="A56" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="B56" s="46"/>
+      <c r="B56" s="45"/>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
       <c r="E56" s="10"/>
@@ -4784,12 +4783,12 @@
       <c r="H56" s="10"/>
       <c r="I56" s="12"/>
       <c r="J56" s="12"/>
-      <c r="K56" s="61"/>
-      <c r="L56" s="47"/>
+      <c r="K56" s="60"/>
+      <c r="L56" s="46"/>
       <c r="M56" s="14"/>
       <c r="N56" s="9"/>
-      <c r="O56" s="24"/>
-      <c r="P56" s="71"/>
+      <c r="O56" s="23"/>
+      <c r="P56" s="70"/>
       <c r="Q56" s="9"/>
       <c r="R56" s="14"/>
       <c r="S56" s="9"/>
@@ -4797,20 +4796,20 @@
       <c r="U56" s="14"/>
       <c r="V56" s="9"/>
       <c r="W56" s="17"/>
-      <c r="X56" s="65"/>
-      <c r="Y56" s="20"/>
-      <c r="Z56" s="20"/>
-      <c r="AA56" s="20"/>
-      <c r="AB56" s="20"/>
-      <c r="AC56" s="20"/>
-      <c r="AD56" s="21"/>
+      <c r="X56" s="64"/>
+      <c r="Y56" s="19"/>
+      <c r="Z56" s="19"/>
+      <c r="AA56" s="19"/>
+      <c r="AB56" s="19"/>
+      <c r="AC56" s="19"/>
+      <c r="AD56" s="20"/>
       <c r="AH56" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C55:F55), 1), BIN2HEX(_xlfn.CONCAT(G55:N55), 2), BIN2HEX(_xlfn.CONCAT(O55:V55), 2), BIN2HEX(_xlfn.CONCAT(W55:AD55), 2) )</f>
         <v>00000FF</v>
       </c>
     </row>
     <row r="57" spans="1:34" ht="32.15" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="48"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
       <c r="E57" s="11"/>
@@ -4819,29 +4818,29 @@
       <c r="H57" s="11"/>
       <c r="I57" s="13"/>
       <c r="J57" s="13"/>
-      <c r="K57" s="62"/>
-      <c r="L57" s="39"/>
+      <c r="K57" s="61"/>
+      <c r="L57" s="38"/>
       <c r="M57" s="15"/>
-      <c r="N57" s="30"/>
-      <c r="O57" s="25"/>
-      <c r="P57" s="72"/>
-      <c r="Q57" s="30"/>
+      <c r="N57" s="29"/>
+      <c r="O57" s="24"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="29"/>
       <c r="R57" s="15"/>
-      <c r="S57" s="30"/>
+      <c r="S57" s="29"/>
       <c r="T57" s="15"/>
       <c r="U57" s="15"/>
-      <c r="V57" s="30"/>
+      <c r="V57" s="29"/>
       <c r="W57" s="18"/>
-      <c r="X57" s="66"/>
-      <c r="Y57" s="31"/>
-      <c r="Z57" s="31"/>
-      <c r="AA57" s="31"/>
-      <c r="AB57" s="31"/>
-      <c r="AC57" s="31"/>
-      <c r="AD57" s="22"/>
+      <c r="X57" s="65"/>
+      <c r="Y57" s="30"/>
+      <c r="Z57" s="30"/>
+      <c r="AA57" s="30"/>
+      <c r="AB57" s="30"/>
+      <c r="AC57" s="30"/>
+      <c r="AD57" s="21"/>
     </row>
     <row r="58" spans="1:34">
-      <c r="A58" s="49" t="s">
+      <c r="A58" s="48" t="s">
         <v>64</v>
       </c>
       <c r="C58" s="11">
@@ -4877,22 +4876,22 @@
       <c r="M58" s="15">
         <v>0</v>
       </c>
-      <c r="N58" s="30">
-        <v>0</v>
-      </c>
-      <c r="O58" s="72">
-        <v>0</v>
-      </c>
-      <c r="P58" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q58" s="30">
+      <c r="N58" s="29">
+        <v>0</v>
+      </c>
+      <c r="O58" s="71">
+        <v>0</v>
+      </c>
+      <c r="P58" s="35">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="29">
         <v>1</v>
       </c>
       <c r="R58" s="15">
         <v>0</v>
       </c>
-      <c r="S58" s="30">
+      <c r="S58" s="29">
         <v>1</v>
       </c>
       <c r="T58" s="15">
@@ -4901,36 +4900,36 @@
       <c r="U58" s="15">
         <v>0</v>
       </c>
-      <c r="V58" s="30">
+      <c r="V58" s="29">
         <v>0</v>
       </c>
       <c r="W58" s="18">
         <v>0</v>
       </c>
-      <c r="X58" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA58" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC58" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD58" s="22">
+      <c r="X58" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA58" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD58" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:34">
-      <c r="A59" s="49" t="s">
+      <c r="A59" s="48" t="s">
         <v>65</v>
       </c>
       <c r="C59" s="11">
@@ -4957,31 +4956,31 @@
       <c r="J59" s="13">
         <v>0</v>
       </c>
-      <c r="K59" s="62">
-        <v>1</v>
-      </c>
-      <c r="L59" s="39">
+      <c r="K59" s="61">
+        <v>1</v>
+      </c>
+      <c r="L59" s="38">
         <v>0</v>
       </c>
       <c r="M59" s="15">
         <v>0</v>
       </c>
-      <c r="N59" s="30">
-        <v>0</v>
-      </c>
-      <c r="O59" s="25">
-        <v>0</v>
-      </c>
-      <c r="P59" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="30">
+      <c r="N59" s="29">
+        <v>0</v>
+      </c>
+      <c r="O59" s="24">
+        <v>0</v>
+      </c>
+      <c r="P59" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="29">
         <v>0</v>
       </c>
       <c r="R59" s="15">
         <v>0</v>
       </c>
-      <c r="S59" s="30">
+      <c r="S59" s="29">
         <v>0</v>
       </c>
       <c r="T59" s="15">
@@ -4990,31 +4989,31 @@
       <c r="U59" s="15">
         <v>1</v>
       </c>
-      <c r="V59" s="30">
+      <c r="V59" s="29">
         <v>1</v>
       </c>
       <c r="W59" s="18">
         <v>0</v>
       </c>
-      <c r="X59" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z59" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC59" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD59" s="22">
+      <c r="X59" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z59" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC59" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD59" s="21">
         <v>1</v>
       </c>
       <c r="AH59" t="str">
@@ -5023,7 +5022,7 @@
       </c>
     </row>
     <row r="60" spans="1:34">
-      <c r="A60" s="49" t="s">
+      <c r="A60" s="48" t="s">
         <v>66</v>
       </c>
       <c r="C60" s="11">
@@ -5050,31 +5049,31 @@
       <c r="J60" s="13">
         <v>0</v>
       </c>
-      <c r="K60" s="62">
-        <v>0</v>
-      </c>
-      <c r="L60" s="39">
+      <c r="K60" s="61">
+        <v>0</v>
+      </c>
+      <c r="L60" s="38">
         <v>0</v>
       </c>
       <c r="M60" s="15">
         <v>0</v>
       </c>
-      <c r="N60" s="30">
-        <v>0</v>
-      </c>
-      <c r="O60" s="25">
-        <v>0</v>
-      </c>
-      <c r="P60" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="30">
+      <c r="N60" s="29">
+        <v>0</v>
+      </c>
+      <c r="O60" s="24">
+        <v>0</v>
+      </c>
+      <c r="P60" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="29">
         <v>0</v>
       </c>
       <c r="R60" s="15">
         <v>0</v>
       </c>
-      <c r="S60" s="30">
+      <c r="S60" s="29">
         <v>0</v>
       </c>
       <c r="T60" s="15">
@@ -5083,31 +5082,31 @@
       <c r="U60" s="15">
         <v>0</v>
       </c>
-      <c r="V60" s="30">
+      <c r="V60" s="29">
         <v>0</v>
       </c>
       <c r="W60" s="18">
         <v>1</v>
       </c>
-      <c r="X60" s="66">
-        <v>1</v>
-      </c>
-      <c r="Y60" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z60" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA60" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB60" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC60" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD60" s="22">
+      <c r="X60" s="65">
+        <v>1</v>
+      </c>
+      <c r="Y60" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z60" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA60" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB60" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC60" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD60" s="21">
         <v>1</v>
       </c>
       <c r="AH60" t="str">
@@ -5116,10 +5115,10 @@
       </c>
     </row>
     <row r="61" spans="1:34" ht="31">
-      <c r="A61" s="52" t="s">
+      <c r="A61" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="B61" s="46"/>
+      <c r="B61" s="45"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
       <c r="E61" s="10"/>
@@ -5132,8 +5131,8 @@
       <c r="L61" s="12"/>
       <c r="M61" s="14"/>
       <c r="N61" s="9"/>
-      <c r="O61" s="24"/>
-      <c r="P61" s="71"/>
+      <c r="O61" s="23"/>
+      <c r="P61" s="70"/>
       <c r="Q61" s="9"/>
       <c r="R61" s="14"/>
       <c r="S61" s="9"/>
@@ -5141,20 +5140,20 @@
       <c r="U61" s="14"/>
       <c r="V61" s="9"/>
       <c r="W61" s="17"/>
-      <c r="X61" s="65"/>
-      <c r="Y61" s="20"/>
-      <c r="Z61" s="20"/>
-      <c r="AA61" s="20"/>
-      <c r="AB61" s="20"/>
-      <c r="AC61" s="20"/>
-      <c r="AD61" s="21"/>
+      <c r="X61" s="64"/>
+      <c r="Y61" s="19"/>
+      <c r="Z61" s="19"/>
+      <c r="AA61" s="19"/>
+      <c r="AB61" s="19"/>
+      <c r="AC61" s="19"/>
+      <c r="AD61" s="20"/>
       <c r="AH61" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C60:F60), 1), BIN2HEX(_xlfn.CONCAT(G60:N60), 2), BIN2HEX(_xlfn.CONCAT(O60:V60), 2), BIN2HEX(_xlfn.CONCAT(W60:AD60), 2) )</f>
         <v>00000FF</v>
       </c>
     </row>
     <row r="62" spans="1:34" ht="32.15" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="48"/>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
       <c r="E62" s="11"/>
@@ -5166,26 +5165,26 @@
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
       <c r="M62" s="15"/>
-      <c r="N62" s="30"/>
-      <c r="O62" s="25"/>
-      <c r="P62" s="72"/>
-      <c r="Q62" s="30"/>
+      <c r="N62" s="29"/>
+      <c r="O62" s="24"/>
+      <c r="P62" s="71"/>
+      <c r="Q62" s="29"/>
       <c r="R62" s="15"/>
-      <c r="S62" s="30"/>
+      <c r="S62" s="29"/>
       <c r="T62" s="15"/>
       <c r="U62" s="15"/>
-      <c r="V62" s="30"/>
+      <c r="V62" s="29"/>
       <c r="W62" s="18"/>
-      <c r="X62" s="66"/>
-      <c r="Y62" s="31"/>
-      <c r="Z62" s="31"/>
-      <c r="AA62" s="31"/>
-      <c r="AB62" s="31"/>
-      <c r="AC62" s="31"/>
-      <c r="AD62" s="22"/>
+      <c r="X62" s="65"/>
+      <c r="Y62" s="30"/>
+      <c r="Z62" s="30"/>
+      <c r="AA62" s="30"/>
+      <c r="AB62" s="30"/>
+      <c r="AC62" s="30"/>
+      <c r="AD62" s="21"/>
     </row>
     <row r="63" spans="1:34">
-      <c r="A63" s="49" t="s">
+      <c r="A63" s="48" t="s">
         <v>68</v>
       </c>
       <c r="C63" s="11">
@@ -5221,22 +5220,22 @@
       <c r="M63" s="15">
         <v>0</v>
       </c>
-      <c r="N63" s="30">
-        <v>0</v>
-      </c>
-      <c r="O63" s="25">
-        <v>0</v>
-      </c>
-      <c r="P63" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="30">
+      <c r="N63" s="29">
+        <v>0</v>
+      </c>
+      <c r="O63" s="24">
+        <v>0</v>
+      </c>
+      <c r="P63" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="29">
         <v>0</v>
       </c>
       <c r="R63" s="15">
         <v>1</v>
       </c>
-      <c r="S63" s="30">
+      <c r="S63" s="29">
         <v>0</v>
       </c>
       <c r="T63" s="15">
@@ -5245,36 +5244,36 @@
       <c r="U63" s="15">
         <v>0</v>
       </c>
-      <c r="V63" s="30">
+      <c r="V63" s="29">
         <v>0</v>
       </c>
       <c r="W63" s="18">
         <v>0</v>
       </c>
-      <c r="X63" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y63" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z63" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA63" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB63" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC63" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD63" s="22">
+      <c r="X63" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA63" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD63" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:34">
-      <c r="A64" s="49" t="s">
+      <c r="A64" s="48" t="s">
         <v>69</v>
       </c>
       <c r="C64" s="11">
@@ -5310,22 +5309,22 @@
       <c r="M64" s="15">
         <v>0</v>
       </c>
-      <c r="N64" s="30">
-        <v>0</v>
-      </c>
-      <c r="O64" s="25">
-        <v>0</v>
-      </c>
-      <c r="P64" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="30">
+      <c r="N64" s="29">
+        <v>0</v>
+      </c>
+      <c r="O64" s="24">
+        <v>0</v>
+      </c>
+      <c r="P64" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="29">
         <v>0</v>
       </c>
       <c r="R64" s="15">
         <v>0</v>
       </c>
-      <c r="S64" s="30">
+      <c r="S64" s="29">
         <v>0</v>
       </c>
       <c r="T64" s="15">
@@ -5334,31 +5333,31 @@
       <c r="U64" s="15">
         <v>0</v>
       </c>
-      <c r="V64" s="30">
+      <c r="V64" s="29">
         <v>0</v>
       </c>
       <c r="W64" s="18">
         <v>1</v>
       </c>
-      <c r="X64" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y64" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z64" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA64" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB64" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC64" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD64" s="22">
+      <c r="X64" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z64" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB64" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD64" s="21">
         <v>1</v>
       </c>
       <c r="AH64" t="str">
@@ -5367,7 +5366,7 @@
       </c>
     </row>
     <row r="65" spans="1:34">
-      <c r="A65" s="49" t="s">
+      <c r="A65" s="48" t="s">
         <v>70</v>
       </c>
       <c r="C65" s="11">
@@ -5403,22 +5402,22 @@
       <c r="M65" s="15">
         <v>0</v>
       </c>
-      <c r="N65" s="30">
-        <v>0</v>
-      </c>
-      <c r="O65" s="25">
-        <v>0</v>
-      </c>
-      <c r="P65" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="30">
+      <c r="N65" s="29">
+        <v>0</v>
+      </c>
+      <c r="O65" s="24">
+        <v>0</v>
+      </c>
+      <c r="P65" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="29">
         <v>0</v>
       </c>
       <c r="R65" s="15">
         <v>0</v>
       </c>
-      <c r="S65" s="30">
+      <c r="S65" s="29">
         <v>0</v>
       </c>
       <c r="T65" s="15">
@@ -5427,31 +5426,31 @@
       <c r="U65" s="15">
         <v>0</v>
       </c>
-      <c r="V65" s="30">
+      <c r="V65" s="29">
         <v>0</v>
       </c>
       <c r="W65" s="18">
         <v>0</v>
       </c>
-      <c r="X65" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y65" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z65" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA65" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB65" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC65" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD65" s="22">
+      <c r="X65" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z65" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA65" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB65" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD65" s="21">
         <v>1</v>
       </c>
       <c r="AH65" t="str">
@@ -5460,7 +5459,7 @@
       </c>
     </row>
     <row r="66" spans="1:34">
-      <c r="A66" s="49" t="s">
+      <c r="A66" s="48" t="s">
         <v>71</v>
       </c>
       <c r="C66" s="11">
@@ -5496,22 +5495,22 @@
       <c r="M66" s="15">
         <v>0</v>
       </c>
-      <c r="N66" s="30">
-        <v>0</v>
-      </c>
-      <c r="O66" s="25">
-        <v>0</v>
-      </c>
-      <c r="P66" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="30">
+      <c r="N66" s="29">
+        <v>0</v>
+      </c>
+      <c r="O66" s="24">
+        <v>0</v>
+      </c>
+      <c r="P66" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="29">
         <v>0</v>
       </c>
       <c r="R66" s="15">
         <v>0</v>
       </c>
-      <c r="S66" s="30">
+      <c r="S66" s="29">
         <v>0</v>
       </c>
       <c r="T66" s="15">
@@ -5520,31 +5519,31 @@
       <c r="U66" s="15">
         <v>1</v>
       </c>
-      <c r="V66" s="30">
+      <c r="V66" s="29">
         <v>1</v>
       </c>
       <c r="W66" s="18">
         <v>0</v>
       </c>
-      <c r="X66" s="66">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z66" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA66" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB66" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC66" s="31">
-        <v>0</v>
-      </c>
-      <c r="AD66" s="22">
+      <c r="X66" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z66" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB66" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC66" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="21">
         <v>1</v>
       </c>
       <c r="AH66" t="str">
@@ -5553,7 +5552,7 @@
       </c>
     </row>
     <row r="67" spans="1:34">
-      <c r="A67" s="49" t="s">
+      <c r="A67" s="48" t="s">
         <v>72</v>
       </c>
       <c r="C67" s="11">
@@ -5589,16 +5588,16 @@
       <c r="M67" s="15">
         <v>0</v>
       </c>
-      <c r="N67" s="30">
-        <v>0</v>
-      </c>
-      <c r="O67" s="26">
-        <v>0</v>
-      </c>
-      <c r="P67" s="73">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="30">
+      <c r="N67" s="29">
+        <v>0</v>
+      </c>
+      <c r="O67" s="25">
+        <v>0</v>
+      </c>
+      <c r="P67" s="72">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="29">
         <v>0</v>
       </c>
       <c r="R67" s="16">
@@ -5613,31 +5612,31 @@
       <c r="U67" s="15">
         <v>0</v>
       </c>
-      <c r="V67" s="30">
+      <c r="V67" s="29">
         <v>0</v>
       </c>
       <c r="W67" s="18">
         <v>1</v>
       </c>
-      <c r="X67" s="66">
-        <v>1</v>
-      </c>
-      <c r="Y67" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z67" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA67" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB67" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC67" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD67" s="22">
+      <c r="X67" s="65">
+        <v>1</v>
+      </c>
+      <c r="Y67" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z67" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA67" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB67" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC67" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD67" s="21">
         <v>1</v>
       </c>
       <c r="AH67" t="str">
@@ -5646,168 +5645,168 @@
       </c>
     </row>
     <row r="68" spans="1:34" ht="31">
-      <c r="A68" s="45" t="s">
+      <c r="A68" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="46"/>
-      <c r="C68" s="68"/>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
-      <c r="H68" s="68"/>
-      <c r="I68" s="24"/>
-      <c r="J68" s="24"/>
-      <c r="K68" s="24"/>
-      <c r="L68" s="24"/>
-      <c r="M68" s="24"/>
-      <c r="N68" s="48"/>
-      <c r="O68" s="25"/>
-      <c r="P68" s="25"/>
-      <c r="Q68" s="71"/>
-      <c r="R68" s="36"/>
-      <c r="S68" s="36"/>
-      <c r="T68" s="24"/>
-      <c r="U68" s="24"/>
-      <c r="V68" s="48"/>
-      <c r="W68" s="24"/>
-      <c r="X68" s="71"/>
-      <c r="Y68" s="20"/>
-      <c r="Z68" s="20"/>
-      <c r="AA68" s="20"/>
-      <c r="AB68" s="20"/>
-      <c r="AC68" s="20"/>
-      <c r="AD68" s="21"/>
+      <c r="B68" s="45"/>
+      <c r="C68" s="67"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="67"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="67"/>
+      <c r="H68" s="67"/>
+      <c r="I68" s="23"/>
+      <c r="J68" s="23"/>
+      <c r="K68" s="23"/>
+      <c r="L68" s="23"/>
+      <c r="M68" s="23"/>
+      <c r="N68" s="47"/>
+      <c r="O68" s="24"/>
+      <c r="P68" s="24"/>
+      <c r="Q68" s="70"/>
+      <c r="R68" s="35"/>
+      <c r="S68" s="35"/>
+      <c r="T68" s="23"/>
+      <c r="U68" s="23"/>
+      <c r="V68" s="47"/>
+      <c r="W68" s="23"/>
+      <c r="X68" s="70"/>
+      <c r="Y68" s="19"/>
+      <c r="Z68" s="19"/>
+      <c r="AA68" s="19"/>
+      <c r="AB68" s="19"/>
+      <c r="AC68" s="19"/>
+      <c r="AD68" s="20"/>
       <c r="AH68" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C67:F67), 1), BIN2HEX(_xlfn.CONCAT(G67:N67), 2), BIN2HEX(_xlfn.CONCAT(O67:V67), 2), BIN2HEX(_xlfn.CONCAT(W67:AD67), 2) )</f>
         <v>00000FF</v>
       </c>
     </row>
     <row r="69" spans="1:34" ht="32.15" customHeight="1">
-      <c r="A69" s="49"/>
-      <c r="C69" s="69"/>
-      <c r="D69" s="69"/>
-      <c r="E69" s="69"/>
-      <c r="F69" s="69"/>
-      <c r="G69" s="69"/>
-      <c r="H69" s="69"/>
-      <c r="I69" s="25"/>
-      <c r="J69" s="25"/>
-      <c r="K69" s="25"/>
-      <c r="L69" s="25"/>
-      <c r="M69" s="25"/>
-      <c r="N69" s="36"/>
-      <c r="O69" s="25"/>
-      <c r="P69" s="25"/>
-      <c r="Q69" s="72"/>
-      <c r="R69" s="36"/>
-      <c r="S69" s="36"/>
-      <c r="T69" s="25"/>
-      <c r="U69" s="25"/>
-      <c r="V69" s="36"/>
-      <c r="W69" s="25"/>
-      <c r="X69" s="72"/>
-      <c r="Y69" s="31"/>
-      <c r="Z69" s="31"/>
-      <c r="AA69" s="31"/>
-      <c r="AB69" s="31"/>
-      <c r="AC69" s="31"/>
-      <c r="AD69" s="22"/>
+      <c r="A69" s="48"/>
+      <c r="C69" s="68"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="68"/>
+      <c r="G69" s="68"/>
+      <c r="H69" s="68"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="24"/>
+      <c r="K69" s="24"/>
+      <c r="L69" s="24"/>
+      <c r="M69" s="24"/>
+      <c r="N69" s="35"/>
+      <c r="O69" s="24"/>
+      <c r="P69" s="24"/>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="35"/>
+      <c r="S69" s="35"/>
+      <c r="T69" s="24"/>
+      <c r="U69" s="24"/>
+      <c r="V69" s="35"/>
+      <c r="W69" s="24"/>
+      <c r="X69" s="71"/>
+      <c r="Y69" s="30"/>
+      <c r="Z69" s="30"/>
+      <c r="AA69" s="30"/>
+      <c r="AB69" s="30"/>
+      <c r="AC69" s="30"/>
+      <c r="AD69" s="21"/>
     </row>
     <row r="70" spans="1:34">
-      <c r="A70" s="49" t="s">
+      <c r="A70" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="C70" s="69">
-        <v>0</v>
-      </c>
-      <c r="D70" s="69">
-        <v>0</v>
-      </c>
-      <c r="E70" s="69">
-        <v>0</v>
-      </c>
-      <c r="F70" s="69">
-        <v>0</v>
-      </c>
-      <c r="G70" s="69">
-        <v>0</v>
-      </c>
-      <c r="H70" s="69">
-        <v>0</v>
-      </c>
-      <c r="I70" s="25">
-        <v>0</v>
-      </c>
-      <c r="J70" s="25">
-        <v>0</v>
-      </c>
-      <c r="K70" s="25">
-        <v>0</v>
-      </c>
-      <c r="L70" s="25">
-        <v>0</v>
-      </c>
-      <c r="M70" s="25">
-        <v>0</v>
-      </c>
-      <c r="N70" s="36">
-        <v>0</v>
-      </c>
-      <c r="O70" s="25">
-        <v>0</v>
-      </c>
-      <c r="P70" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="73">
-        <v>0</v>
-      </c>
-      <c r="R70" s="36">
-        <v>0</v>
-      </c>
-      <c r="S70" s="36">
-        <v>0</v>
-      </c>
-      <c r="T70" s="25">
-        <v>0</v>
-      </c>
-      <c r="U70" s="25">
-        <v>0</v>
-      </c>
-      <c r="V70" s="36">
-        <v>0</v>
-      </c>
-      <c r="W70" s="25">
-        <v>0</v>
-      </c>
-      <c r="X70" s="72">
-        <v>0</v>
-      </c>
-      <c r="Y70" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z70" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA70" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB70" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC70" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD70" s="22">
+      <c r="C70" s="68">
+        <v>0</v>
+      </c>
+      <c r="D70" s="68">
+        <v>0</v>
+      </c>
+      <c r="E70" s="68">
+        <v>0</v>
+      </c>
+      <c r="F70" s="68">
+        <v>0</v>
+      </c>
+      <c r="G70" s="68">
+        <v>0</v>
+      </c>
+      <c r="H70" s="68">
+        <v>0</v>
+      </c>
+      <c r="I70" s="24">
+        <v>0</v>
+      </c>
+      <c r="J70" s="24">
+        <v>0</v>
+      </c>
+      <c r="K70" s="24">
+        <v>0</v>
+      </c>
+      <c r="L70" s="24">
+        <v>0</v>
+      </c>
+      <c r="M70" s="24">
+        <v>0</v>
+      </c>
+      <c r="N70" s="35">
+        <v>0</v>
+      </c>
+      <c r="O70" s="24">
+        <v>0</v>
+      </c>
+      <c r="P70" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="72">
+        <v>0</v>
+      </c>
+      <c r="R70" s="35">
+        <v>0</v>
+      </c>
+      <c r="S70" s="35">
+        <v>0</v>
+      </c>
+      <c r="T70" s="24">
+        <v>0</v>
+      </c>
+      <c r="U70" s="24">
+        <v>0</v>
+      </c>
+      <c r="V70" s="35">
+        <v>0</v>
+      </c>
+      <c r="W70" s="24">
+        <v>0</v>
+      </c>
+      <c r="X70" s="71">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB70" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC70" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD70" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:34" ht="31">
-      <c r="A71" s="27" t="s">
+      <c r="A71" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="B71" s="53"/>
+      <c r="B71" s="52"/>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
       <c r="E71" s="10"/>
@@ -5820,30 +5819,30 @@
       <c r="L71" s="12"/>
       <c r="M71" s="14"/>
       <c r="N71" s="9"/>
-      <c r="O71" s="24"/>
-      <c r="P71" s="71"/>
-      <c r="Q71" s="30"/>
+      <c r="O71" s="23"/>
+      <c r="P71" s="70"/>
+      <c r="Q71" s="29"/>
       <c r="R71" s="14"/>
       <c r="S71" s="9"/>
       <c r="T71" s="14"/>
       <c r="U71" s="14"/>
       <c r="V71" s="9"/>
       <c r="W71" s="17"/>
-      <c r="X71" s="65"/>
-      <c r="Y71" s="20"/>
-      <c r="Z71" s="20"/>
-      <c r="AA71" s="20"/>
-      <c r="AB71" s="20"/>
-      <c r="AC71" s="20"/>
-      <c r="AD71" s="21"/>
+      <c r="X71" s="64"/>
+      <c r="Y71" s="19"/>
+      <c r="Z71" s="19"/>
+      <c r="AA71" s="19"/>
+      <c r="AB71" s="19"/>
+      <c r="AC71" s="19"/>
+      <c r="AD71" s="20"/>
       <c r="AH71" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C70:F70), 1), BIN2HEX(_xlfn.CONCAT(G70:N70), 2), BIN2HEX(_xlfn.CONCAT(O70:V70), 2), BIN2HEX(_xlfn.CONCAT(W70:AD70), 2) )</f>
         <v>000000F</v>
       </c>
     </row>
     <row r="72" spans="1:34" ht="31">
-      <c r="A72" s="28"/>
-      <c r="B72" s="29"/>
+      <c r="A72" s="27"/>
+      <c r="B72" s="28"/>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
       <c r="E72" s="11"/>
@@ -5855,29 +5854,29 @@
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
       <c r="M72" s="15"/>
-      <c r="N72" s="30"/>
-      <c r="O72" s="25"/>
-      <c r="P72" s="72"/>
-      <c r="Q72" s="30"/>
+      <c r="N72" s="29"/>
+      <c r="O72" s="24"/>
+      <c r="P72" s="71"/>
+      <c r="Q72" s="29"/>
       <c r="R72" s="15"/>
-      <c r="S72" s="30"/>
+      <c r="S72" s="29"/>
       <c r="T72" s="15"/>
       <c r="U72" s="15"/>
-      <c r="V72" s="30"/>
+      <c r="V72" s="29"/>
       <c r="W72" s="18"/>
-      <c r="X72" s="66"/>
-      <c r="Y72" s="31"/>
-      <c r="Z72" s="31"/>
-      <c r="AA72" s="31"/>
-      <c r="AB72" s="31"/>
-      <c r="AC72" s="31"/>
-      <c r="AD72" s="22"/>
+      <c r="X72" s="65"/>
+      <c r="Y72" s="30"/>
+      <c r="Z72" s="30"/>
+      <c r="AA72" s="30"/>
+      <c r="AB72" s="30"/>
+      <c r="AC72" s="30"/>
+      <c r="AD72" s="21"/>
     </row>
     <row r="73" spans="1:34">
-      <c r="A73" s="32" t="s">
+      <c r="A73" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="29"/>
+      <c r="B73" s="28"/>
       <c r="C73" s="11">
         <v>0</v>
       </c>
@@ -5911,47 +5910,63 @@
       <c r="M73" s="15">
         <v>0</v>
       </c>
-      <c r="N73" s="30">
-        <v>0</v>
-      </c>
-      <c r="O73" s="25">
-        <v>0</v>
-      </c>
-      <c r="P73" s="72">
-        <v>1</v>
-      </c>
-      <c r="Q73" s="30"/>
-      <c r="R73" s="15"/>
-      <c r="S73" s="30"/>
-      <c r="T73" s="15"/>
-      <c r="U73" s="15"/>
-      <c r="V73" s="30"/>
-      <c r="W73" s="18"/>
-      <c r="X73" s="66"/>
-      <c r="Y73" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z73" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA73" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB73" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC73" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD73" s="22">
+      <c r="N73" s="29">
+        <v>0</v>
+      </c>
+      <c r="O73" s="24">
+        <v>0</v>
+      </c>
+      <c r="P73" s="71">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="29">
+        <v>0</v>
+      </c>
+      <c r="R73" s="15">
+        <v>0</v>
+      </c>
+      <c r="S73" s="29">
+        <v>0</v>
+      </c>
+      <c r="T73" s="15">
+        <v>0</v>
+      </c>
+      <c r="U73" s="15">
+        <v>0</v>
+      </c>
+      <c r="V73" s="29">
+        <v>0</v>
+      </c>
+      <c r="W73" s="18">
+        <v>0</v>
+      </c>
+      <c r="X73" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA73" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB73" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC73" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD73" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:34">
-      <c r="A74" s="32" t="s">
+      <c r="A74" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="29"/>
+      <c r="B74" s="28"/>
       <c r="C74" s="11">
         <v>0</v>
       </c>
@@ -5985,51 +6000,67 @@
       <c r="M74" s="15">
         <v>0</v>
       </c>
-      <c r="N74" s="30">
-        <v>0</v>
-      </c>
-      <c r="O74" s="25">
-        <v>0</v>
-      </c>
-      <c r="P74" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="30"/>
-      <c r="R74" s="15"/>
-      <c r="S74" s="30"/>
-      <c r="T74" s="15"/>
-      <c r="U74" s="15"/>
-      <c r="V74" s="30"/>
-      <c r="W74" s="18"/>
-      <c r="X74" s="66"/>
-      <c r="Y74" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z74" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA74" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB74" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC74" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD74" s="22">
+      <c r="N74" s="29">
+        <v>0</v>
+      </c>
+      <c r="O74" s="24">
+        <v>0</v>
+      </c>
+      <c r="P74" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="29">
+        <v>0</v>
+      </c>
+      <c r="R74" s="15">
+        <v>0</v>
+      </c>
+      <c r="S74" s="29">
+        <v>0</v>
+      </c>
+      <c r="T74" s="15">
+        <v>0</v>
+      </c>
+      <c r="U74" s="15">
+        <v>0</v>
+      </c>
+      <c r="V74" s="29">
+        <v>0</v>
+      </c>
+      <c r="W74" s="18">
+        <v>0</v>
+      </c>
+      <c r="X74" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA74" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB74" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC74" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD74" s="21">
         <v>1</v>
       </c>
       <c r="AH74" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C73:F73), 1), BIN2HEX(_xlfn.CONCAT(G73:N73), 2), BIN2HEX(_xlfn.CONCAT(O73:V73), 2), BIN2HEX(_xlfn.CONCAT(W73:AD73), 2) )</f>
-        <v>000011E</v>
+        <v>000401E</v>
       </c>
     </row>
     <row r="75" spans="1:34">
-      <c r="A75" s="32" t="s">
+      <c r="A75" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="29"/>
+      <c r="B75" s="28"/>
       <c r="C75" s="11">
         <v>0</v>
       </c>
@@ -6063,39 +6094,55 @@
       <c r="M75" s="15">
         <v>0</v>
       </c>
-      <c r="N75" s="30">
-        <v>0</v>
-      </c>
-      <c r="O75" s="25">
-        <v>0</v>
-      </c>
-      <c r="P75" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="30"/>
-      <c r="R75" s="15"/>
-      <c r="S75" s="30"/>
-      <c r="T75" s="15"/>
-      <c r="U75" s="15"/>
-      <c r="V75" s="30"/>
-      <c r="W75" s="18"/>
-      <c r="X75" s="66"/>
-      <c r="Y75" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z75" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA75" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB75" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC75" s="31">
-        <v>0</v>
-      </c>
-      <c r="AD75" s="22">
+      <c r="N75" s="29">
+        <v>0</v>
+      </c>
+      <c r="O75" s="24">
+        <v>0</v>
+      </c>
+      <c r="P75" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="29">
+        <v>0</v>
+      </c>
+      <c r="R75" s="15">
+        <v>0</v>
+      </c>
+      <c r="S75" s="29">
+        <v>0</v>
+      </c>
+      <c r="T75" s="15">
+        <v>0</v>
+      </c>
+      <c r="U75" s="15">
+        <v>0</v>
+      </c>
+      <c r="V75" s="29">
+        <v>0</v>
+      </c>
+      <c r="W75" s="18">
+        <v>0</v>
+      </c>
+      <c r="X75" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z75" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="21">
         <v>1</v>
       </c>
       <c r="AH75" t="str">
@@ -6104,10 +6151,10 @@
       </c>
     </row>
     <row r="76" spans="1:34">
-      <c r="A76" s="32" t="s">
+      <c r="A76" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="29"/>
+      <c r="B76" s="28"/>
       <c r="C76" s="11">
         <v>0</v>
       </c>
@@ -6141,39 +6188,55 @@
       <c r="M76" s="15">
         <v>0</v>
       </c>
-      <c r="N76" s="30">
-        <v>0</v>
-      </c>
-      <c r="O76" s="25">
-        <v>0</v>
-      </c>
-      <c r="P76" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="30"/>
-      <c r="R76" s="15"/>
-      <c r="S76" s="30"/>
-      <c r="T76" s="15"/>
-      <c r="U76" s="15"/>
-      <c r="V76" s="30"/>
-      <c r="W76" s="18"/>
-      <c r="X76" s="66"/>
-      <c r="Y76" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z76" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA76" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB76" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC76" s="31">
-        <v>1</v>
-      </c>
-      <c r="AD76" s="22">
+      <c r="N76" s="29">
+        <v>0</v>
+      </c>
+      <c r="O76" s="24">
+        <v>0</v>
+      </c>
+      <c r="P76" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="29">
+        <v>0</v>
+      </c>
+      <c r="R76" s="15">
+        <v>0</v>
+      </c>
+      <c r="S76" s="29">
+        <v>0</v>
+      </c>
+      <c r="T76" s="15">
+        <v>0</v>
+      </c>
+      <c r="U76" s="15">
+        <v>0</v>
+      </c>
+      <c r="V76" s="29">
+        <v>0</v>
+      </c>
+      <c r="W76" s="18">
+        <v>0</v>
+      </c>
+      <c r="X76" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z76" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA76" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB76" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC76" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD76" s="21">
         <v>1</v>
       </c>
       <c r="AH76" t="str">
@@ -6182,8 +6245,8 @@
       </c>
     </row>
     <row r="77" spans="1:34">
-      <c r="A77" s="32"/>
-      <c r="B77" s="29"/>
+      <c r="A77" s="31"/>
+      <c r="B77" s="28"/>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
       <c r="E77" s="11"/>
@@ -6195,33 +6258,33 @@
       <c r="K77" s="13"/>
       <c r="L77" s="13"/>
       <c r="M77" s="15"/>
-      <c r="N77" s="30"/>
-      <c r="O77" s="25"/>
-      <c r="P77" s="72"/>
-      <c r="Q77" s="30"/>
+      <c r="N77" s="29"/>
+      <c r="O77" s="24"/>
+      <c r="P77" s="71"/>
+      <c r="Q77" s="29"/>
       <c r="R77" s="15"/>
-      <c r="S77" s="30"/>
+      <c r="S77" s="29"/>
       <c r="T77" s="15"/>
       <c r="U77" s="15"/>
-      <c r="V77" s="30"/>
+      <c r="V77" s="29"/>
       <c r="W77" s="18"/>
-      <c r="X77" s="67"/>
-      <c r="Y77" s="31"/>
-      <c r="Z77" s="31"/>
-      <c r="AA77" s="31"/>
-      <c r="AB77" s="31"/>
-      <c r="AC77" s="31"/>
-      <c r="AD77" s="22"/>
+      <c r="X77" s="66"/>
+      <c r="Y77" s="30"/>
+      <c r="Z77" s="30"/>
+      <c r="AA77" s="30"/>
+      <c r="AB77" s="30"/>
+      <c r="AC77" s="30"/>
+      <c r="AD77" s="21"/>
       <c r="AH77" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C76:F76), 1), BIN2HEX(_xlfn.CONCAT(G76:N76), 2), BIN2HEX(_xlfn.CONCAT(O76:V76), 2), BIN2HEX(_xlfn.CONCAT(W76:AD76), 2) )</f>
         <v>000003F</v>
       </c>
     </row>
     <row r="78" spans="1:34" ht="31">
-      <c r="A78" s="27" t="s">
+      <c r="A78" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="B78" s="53"/>
+      <c r="B78" s="52"/>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
       <c r="E78" s="10"/>
@@ -6234,8 +6297,8 @@
       <c r="L78" s="12"/>
       <c r="M78" s="14"/>
       <c r="N78" s="9"/>
-      <c r="O78" s="24"/>
-      <c r="P78" s="71"/>
+      <c r="O78" s="23"/>
+      <c r="P78" s="70"/>
       <c r="Q78" s="9"/>
       <c r="R78" s="14"/>
       <c r="S78" s="9"/>
@@ -6243,17 +6306,17 @@
       <c r="U78" s="14"/>
       <c r="V78" s="9"/>
       <c r="W78" s="17"/>
-      <c r="X78" s="66"/>
-      <c r="Y78" s="20"/>
-      <c r="Z78" s="20"/>
-      <c r="AA78" s="20"/>
-      <c r="AB78" s="20"/>
-      <c r="AC78" s="20"/>
-      <c r="AD78" s="21"/>
+      <c r="X78" s="65"/>
+      <c r="Y78" s="19"/>
+      <c r="Z78" s="19"/>
+      <c r="AA78" s="19"/>
+      <c r="AB78" s="19"/>
+      <c r="AC78" s="19"/>
+      <c r="AD78" s="20"/>
     </row>
     <row r="79" spans="1:34" ht="31">
-      <c r="A79" s="28"/>
-      <c r="B79" s="29"/>
+      <c r="A79" s="27"/>
+      <c r="B79" s="28"/>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
       <c r="E79" s="11"/>
@@ -6265,29 +6328,29 @@
       <c r="K79" s="13"/>
       <c r="L79" s="13"/>
       <c r="M79" s="15"/>
-      <c r="N79" s="30"/>
-      <c r="O79" s="25"/>
-      <c r="P79" s="72"/>
-      <c r="Q79" s="30"/>
+      <c r="N79" s="29"/>
+      <c r="O79" s="24"/>
+      <c r="P79" s="71"/>
+      <c r="Q79" s="29"/>
       <c r="R79" s="15"/>
-      <c r="S79" s="30"/>
+      <c r="S79" s="29"/>
       <c r="T79" s="15"/>
       <c r="U79" s="15"/>
-      <c r="V79" s="30"/>
+      <c r="V79" s="29"/>
       <c r="W79" s="18"/>
-      <c r="X79" s="66"/>
-      <c r="Y79" s="31"/>
-      <c r="Z79" s="31"/>
-      <c r="AA79" s="31"/>
-      <c r="AB79" s="31"/>
-      <c r="AC79" s="31"/>
-      <c r="AD79" s="22"/>
+      <c r="X79" s="65"/>
+      <c r="Y79" s="30"/>
+      <c r="Z79" s="30"/>
+      <c r="AA79" s="30"/>
+      <c r="AB79" s="30"/>
+      <c r="AC79" s="30"/>
+      <c r="AD79" s="21"/>
     </row>
     <row r="80" spans="1:34">
-      <c r="A80" s="32" t="s">
+      <c r="A80" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="29"/>
+      <c r="B80" s="28"/>
       <c r="C80" s="11">
         <v>0</v>
       </c>
@@ -6321,47 +6384,63 @@
       <c r="M80" s="15">
         <v>0</v>
       </c>
-      <c r="N80" s="30">
-        <v>0</v>
-      </c>
-      <c r="O80" s="25">
-        <v>0</v>
-      </c>
-      <c r="P80" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="30"/>
-      <c r="R80" s="15"/>
-      <c r="S80" s="30"/>
-      <c r="T80" s="15"/>
-      <c r="U80" s="15"/>
-      <c r="V80" s="30"/>
-      <c r="W80" s="18"/>
-      <c r="X80" s="66"/>
-      <c r="Y80" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z80" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA80" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC80" s="31">
-        <v>0</v>
-      </c>
-      <c r="AD80" s="22">
+      <c r="N80" s="29">
+        <v>0</v>
+      </c>
+      <c r="O80" s="24">
+        <v>0</v>
+      </c>
+      <c r="P80" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="29">
+        <v>0</v>
+      </c>
+      <c r="R80" s="15">
+        <v>0</v>
+      </c>
+      <c r="S80" s="29">
+        <v>0</v>
+      </c>
+      <c r="T80" s="15">
+        <v>0</v>
+      </c>
+      <c r="U80" s="15">
+        <v>0</v>
+      </c>
+      <c r="V80" s="29">
+        <v>0</v>
+      </c>
+      <c r="W80" s="18">
+        <v>0</v>
+      </c>
+      <c r="X80" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA80" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:36">
-      <c r="A81" s="32" t="s">
+      <c r="A81" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="29"/>
+      <c r="B81" s="28"/>
       <c r="C81" s="11">
         <v>0</v>
       </c>
@@ -6395,39 +6474,55 @@
       <c r="M81" s="15">
         <v>0</v>
       </c>
-      <c r="N81" s="30">
-        <v>0</v>
-      </c>
-      <c r="O81" s="25">
-        <v>0</v>
-      </c>
-      <c r="P81" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="30"/>
-      <c r="R81" s="15"/>
-      <c r="S81" s="30"/>
-      <c r="T81" s="15"/>
-      <c r="U81" s="15"/>
-      <c r="V81" s="30"/>
-      <c r="W81" s="18"/>
-      <c r="X81" s="66"/>
-      <c r="Y81" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z81" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA81" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB81" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC81" s="31">
-        <v>0</v>
-      </c>
-      <c r="AD81" s="22">
+      <c r="N81" s="29">
+        <v>0</v>
+      </c>
+      <c r="O81" s="24">
+        <v>0</v>
+      </c>
+      <c r="P81" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="29">
+        <v>0</v>
+      </c>
+      <c r="R81" s="15">
+        <v>0</v>
+      </c>
+      <c r="S81" s="29">
+        <v>0</v>
+      </c>
+      <c r="T81" s="15">
+        <v>0</v>
+      </c>
+      <c r="U81" s="15">
+        <v>0</v>
+      </c>
+      <c r="V81" s="29">
+        <v>0</v>
+      </c>
+      <c r="W81" s="18">
+        <v>0</v>
+      </c>
+      <c r="X81" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA81" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC81" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="21">
         <v>1</v>
       </c>
       <c r="AH81" t="str">
@@ -6436,10 +6531,10 @@
       </c>
     </row>
     <row r="82" spans="1:36">
-      <c r="A82" s="32" t="s">
+      <c r="A82" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="29"/>
+      <c r="B82" s="28"/>
       <c r="C82" s="11">
         <v>0</v>
       </c>
@@ -6473,39 +6568,55 @@
       <c r="M82" s="15">
         <v>0</v>
       </c>
-      <c r="N82" s="30">
-        <v>0</v>
-      </c>
-      <c r="O82" s="25">
-        <v>0</v>
-      </c>
-      <c r="P82" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="30"/>
-      <c r="R82" s="15"/>
-      <c r="S82" s="30"/>
-      <c r="T82" s="15"/>
-      <c r="U82" s="15"/>
-      <c r="V82" s="30"/>
-      <c r="W82" s="18"/>
-      <c r="X82" s="66"/>
-      <c r="Y82" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z82" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA82" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB82" s="31">
-        <v>0</v>
-      </c>
-      <c r="AC82" s="31">
-        <v>0</v>
-      </c>
-      <c r="AD82" s="22">
+      <c r="N82" s="29">
+        <v>0</v>
+      </c>
+      <c r="O82" s="24">
+        <v>0</v>
+      </c>
+      <c r="P82" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="29">
+        <v>0</v>
+      </c>
+      <c r="R82" s="15">
+        <v>0</v>
+      </c>
+      <c r="S82" s="29">
+        <v>0</v>
+      </c>
+      <c r="T82" s="15">
+        <v>0</v>
+      </c>
+      <c r="U82" s="15">
+        <v>0</v>
+      </c>
+      <c r="V82" s="29">
+        <v>0</v>
+      </c>
+      <c r="W82" s="18">
+        <v>0</v>
+      </c>
+      <c r="X82" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA82" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB82" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="21">
         <v>1</v>
       </c>
       <c r="AH82" t="str">
@@ -6514,10 +6625,10 @@
       </c>
     </row>
     <row r="83" spans="1:36">
-      <c r="A83" s="32" t="s">
+      <c r="A83" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="29"/>
+      <c r="B83" s="28"/>
       <c r="C83" s="11">
         <v>0</v>
       </c>
@@ -6551,39 +6662,55 @@
       <c r="M83" s="15">
         <v>0</v>
       </c>
-      <c r="N83" s="30">
-        <v>0</v>
-      </c>
-      <c r="O83" s="25">
-        <v>0</v>
-      </c>
-      <c r="P83" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="30"/>
-      <c r="R83" s="15"/>
-      <c r="S83" s="30"/>
-      <c r="T83" s="15"/>
-      <c r="U83" s="15"/>
-      <c r="V83" s="30"/>
-      <c r="W83" s="18"/>
-      <c r="X83" s="66"/>
-      <c r="Y83" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA83" s="31">
-        <v>1</v>
-      </c>
-      <c r="AB83" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC83" s="31">
-        <v>0</v>
-      </c>
-      <c r="AD83" s="22">
+      <c r="N83" s="29">
+        <v>0</v>
+      </c>
+      <c r="O83" s="24">
+        <v>0</v>
+      </c>
+      <c r="P83" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="29">
+        <v>0</v>
+      </c>
+      <c r="R83" s="15">
+        <v>0</v>
+      </c>
+      <c r="S83" s="29">
+        <v>0</v>
+      </c>
+      <c r="T83" s="15">
+        <v>0</v>
+      </c>
+      <c r="U83" s="15">
+        <v>0</v>
+      </c>
+      <c r="V83" s="29">
+        <v>0</v>
+      </c>
+      <c r="W83" s="18">
+        <v>0</v>
+      </c>
+      <c r="X83" s="65">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA83" s="30">
+        <v>1</v>
+      </c>
+      <c r="AB83" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC83" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="21">
         <v>0</v>
       </c>
       <c r="AH83" t="str">
@@ -6592,10 +6719,10 @@
       </c>
     </row>
     <row r="84" spans="1:36">
-      <c r="A84" s="33" t="s">
+      <c r="A84" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="34"/>
+      <c r="B84" s="33"/>
       <c r="C84" s="11">
         <v>0</v>
       </c>
@@ -6629,23 +6756,39 @@
       <c r="M84" s="15">
         <v>0</v>
       </c>
-      <c r="N84" s="30">
-        <v>0</v>
-      </c>
-      <c r="O84" s="26">
-        <v>0</v>
-      </c>
-      <c r="P84" s="73">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="7"/>
-      <c r="R84" s="16"/>
-      <c r="S84" s="7"/>
-      <c r="T84" s="16"/>
-      <c r="U84" s="16"/>
-      <c r="V84" s="7"/>
-      <c r="W84" s="19"/>
-      <c r="X84" s="67"/>
+      <c r="N84" s="29">
+        <v>0</v>
+      </c>
+      <c r="O84" s="25">
+        <v>0</v>
+      </c>
+      <c r="P84" s="72">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="29">
+        <v>0</v>
+      </c>
+      <c r="R84" s="15">
+        <v>0</v>
+      </c>
+      <c r="S84" s="29">
+        <v>0</v>
+      </c>
+      <c r="T84" s="15">
+        <v>0</v>
+      </c>
+      <c r="U84" s="15">
+        <v>0</v>
+      </c>
+      <c r="V84" s="29">
+        <v>0</v>
+      </c>
+      <c r="W84" s="18">
+        <v>0</v>
+      </c>
+      <c r="X84" s="65">
+        <v>0</v>
+      </c>
       <c r="Y84" s="8">
         <v>1</v>
       </c>
@@ -6661,7 +6804,7 @@
       <c r="AC84" s="8">
         <v>1</v>
       </c>
-      <c r="AD84" s="23">
+      <c r="AD84" s="22">
         <v>1</v>
       </c>
       <c r="AH84" t="str">
@@ -6672,36 +6815,36 @@
       <c r="AJ84" s="5"/>
     </row>
     <row r="85" spans="1:36">
-      <c r="A85" s="31"/>
-      <c r="B85" s="31"/>
-      <c r="C85" s="31"/>
-      <c r="D85" s="31"/>
-      <c r="E85" s="31"/>
-      <c r="F85" s="31"/>
-      <c r="G85" s="31"/>
-      <c r="H85" s="31"/>
-      <c r="I85" s="31"/>
-      <c r="J85" s="31"/>
-      <c r="K85" s="31"/>
-      <c r="L85" s="31"/>
-      <c r="M85" s="31"/>
-      <c r="N85" s="31"/>
-      <c r="O85" s="36"/>
-      <c r="P85" s="36"/>
-      <c r="Q85" s="31"/>
-      <c r="R85" s="31"/>
-      <c r="S85" s="31"/>
-      <c r="T85" s="31"/>
-      <c r="U85" s="31"/>
-      <c r="V85" s="31"/>
-      <c r="W85" s="31"/>
-      <c r="X85" s="31"/>
-      <c r="Y85" s="31"/>
-      <c r="Z85" s="31"/>
-      <c r="AA85" s="31"/>
-      <c r="AB85" s="31"/>
-      <c r="AC85" s="31"/>
-      <c r="AD85" s="31"/>
+      <c r="A85" s="30"/>
+      <c r="B85" s="30"/>
+      <c r="C85" s="30"/>
+      <c r="D85" s="30"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="30"/>
+      <c r="H85" s="30"/>
+      <c r="I85" s="30"/>
+      <c r="J85" s="30"/>
+      <c r="K85" s="30"/>
+      <c r="L85" s="30"/>
+      <c r="M85" s="30"/>
+      <c r="N85" s="30"/>
+      <c r="O85" s="35"/>
+      <c r="P85" s="35"/>
+      <c r="Q85" s="30"/>
+      <c r="R85" s="30"/>
+      <c r="S85" s="30"/>
+      <c r="T85" s="30"/>
+      <c r="U85" s="30"/>
+      <c r="V85" s="30"/>
+      <c r="W85" s="30"/>
+      <c r="X85" s="30"/>
+      <c r="Y85" s="30"/>
+      <c r="Z85" s="30"/>
+      <c r="AA85" s="30"/>
+      <c r="AB85" s="30"/>
+      <c r="AC85" s="30"/>
+      <c r="AD85" s="30"/>
       <c r="AH85" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C84:F84), 1), BIN2HEX(_xlfn.CONCAT(G84:N84), 2), BIN2HEX(_xlfn.CONCAT(O84:V84), 2), BIN2HEX(_xlfn.CONCAT(W84:AD84), 2) )</f>
         <v>000003F</v>
@@ -6866,7 +7009,7 @@
       </c>
       <c r="D9" s="6" t="str">
         <f>microcode!AH74</f>
-        <v>000011E</v>
+        <v>000401E</v>
       </c>
       <c r="F9" t="s">
         <v>88</v>

--- a/hw04/hw04/microcode.xlsx
+++ b/hw04/hw04/microcode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huan\Documents\GT\Summer 2023\CS_2110\hw04\hw04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruh\Documents\GT\Summer 2023\CS_2110\hw04\hw04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9E7A07-EAEA-47F1-A105-F0FE5CA3E72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D92551-0C40-45C2-846E-22BE8C6F3C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="microcode" sheetId="1" r:id="rId1"/>
@@ -25,8 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -1123,14 +1121,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BW86"/>
-  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11.296875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="22.08203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="30" width="4.58203125" customWidth="1"/>
-    <col min="31" max="31" width="2.58203125" customWidth="1"/>
+    <col min="1" max="1" width="22.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="30" width="4.59765625" customWidth="1"/>
+    <col min="31" max="31" width="2.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75" ht="88">
+    <row r="1" spans="1:75" ht="87">
       <c r="A1" s="41"/>
       <c r="B1" s="42"/>
       <c r="C1" s="55" t="s">
@@ -1254,7 +1252,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:75" ht="32.15" customHeight="1">
+    <row r="3" spans="1:75" ht="32.1" customHeight="1">
       <c r="A3" s="46" t="s">
         <v>23</v>
       </c>
@@ -1600,7 +1598,7 @@
         <v>2100038</v>
       </c>
     </row>
-    <row r="8" spans="1:75" ht="32.15" customHeight="1">
+    <row r="8" spans="1:75" ht="32.1" customHeight="1">
       <c r="A8" s="27" t="s">
         <v>27</v>
       </c>
@@ -1758,7 +1756,7 @@
         <v>0000020</v>
       </c>
     </row>
-    <row r="11" spans="1:75" ht="32.15" customHeight="1">
+    <row r="11" spans="1:75" ht="32.1" customHeight="1">
       <c r="A11" s="46" t="s">
         <v>28</v>
       </c>
@@ -1792,7 +1790,7 @@
       <c r="AC11" s="19"/>
       <c r="AD11" s="20"/>
     </row>
-    <row r="12" spans="1:75" ht="16" customHeight="1">
+    <row r="12" spans="1:75" ht="16.05" customHeight="1">
       <c r="A12" s="51"/>
       <c r="C12" s="62"/>
       <c r="D12" s="62"/>
@@ -1954,7 +1952,7 @@
       <c r="BV13" s="4"/>
       <c r="BW13" s="4"/>
     </row>
-    <row r="14" spans="1:75" ht="32.15" customHeight="1">
+    <row r="14" spans="1:75" ht="32.1" customHeight="1">
       <c r="A14" s="46" t="s">
         <v>30</v>
       </c>
@@ -2190,7 +2188,7 @@
         <v>188413F</v>
       </c>
     </row>
-    <row r="17" spans="1:34" ht="32.15" customHeight="1">
+    <row r="17" spans="1:34" ht="32.1" customHeight="1">
       <c r="A17" s="46" t="s">
         <v>32</v>
       </c>
@@ -2441,7 +2439,7 @@
         <v>041103F</v>
       </c>
     </row>
-    <row r="21" spans="1:34" ht="32.15" customHeight="1">
+    <row r="21" spans="1:34" ht="32.1" customHeight="1">
       <c r="A21" s="52" t="s">
         <v>35</v>
       </c>
@@ -2541,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="26">
         <v>0</v>
@@ -2556,19 +2554,19 @@
         <v>1</v>
       </c>
       <c r="R23" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" s="15">
         <v>0</v>
       </c>
       <c r="U23" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="18">
         <v>0</v>
@@ -2596,10 +2594,10 @@
       </c>
       <c r="AH23" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C23:F23), 1), BIN2HEX(_xlfn.CONCAT(G23:N23), 2), BIN2HEX(_xlfn.CONCAT(O23:V23), 2), BIN2HEX(_xlfn.CONCAT(W23:AD23), 2) )</f>
-        <v>049783F</v>
-      </c>
-    </row>
-    <row r="24" spans="1:34" ht="32.15" customHeight="1">
+        <v>04A633F</v>
+      </c>
+    </row>
+    <row r="24" spans="1:34" ht="32.1" customHeight="1">
       <c r="A24" s="46" t="s">
         <v>37</v>
       </c>
@@ -2943,7 +2941,7 @@
         <v>161E03F</v>
       </c>
     </row>
-    <row r="29" spans="1:34" ht="32.15" customHeight="1">
+    <row r="29" spans="1:34" ht="32.1" customHeight="1">
       <c r="A29" s="46" t="s">
         <v>41</v>
       </c>
@@ -3287,7 +3285,7 @@
         <v>190003F</v>
       </c>
     </row>
-    <row r="34" spans="1:34" ht="32.15" customHeight="1">
+    <row r="34" spans="1:34" ht="32.1" customHeight="1">
       <c r="A34" s="46" t="s">
         <v>45</v>
       </c>
@@ -3817,7 +3815,7 @@
         <v>190003F</v>
       </c>
     </row>
-    <row r="41" spans="1:34" ht="32.15" customHeight="1">
+    <row r="41" spans="1:34" ht="32.1" customHeight="1">
       <c r="A41" s="46" t="s">
         <v>51</v>
       </c>
@@ -4161,7 +4159,7 @@
         <v>190003F</v>
       </c>
     </row>
-    <row r="46" spans="1:34" ht="32.15" customHeight="1">
+    <row r="46" spans="1:34" ht="32.1" customHeight="1">
       <c r="A46" s="46" t="s">
         <v>55</v>
       </c>
@@ -4276,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="R48" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" s="15">
         <v>1</v>
@@ -4316,10 +4314,10 @@
       </c>
       <c r="AH48" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C48:F48), 1), BIN2HEX(_xlfn.CONCAT(G48:N48), 2), BIN2HEX(_xlfn.CONCAT(O48:V48), 2), BIN2HEX(_xlfn.CONCAT(W48:AD48), 2) )</f>
-        <v>1040C3F</v>
-      </c>
-    </row>
-    <row r="49" spans="1:34" ht="32.15" customHeight="1">
+        <v>104143F</v>
+      </c>
+    </row>
+    <row r="49" spans="1:34" ht="32.1" customHeight="1">
       <c r="A49" s="46" t="s">
         <v>57</v>
       </c>
@@ -4477,7 +4475,7 @@
         <v>188423F</v>
       </c>
     </row>
-    <row r="52" spans="1:34" ht="32.15" customHeight="1">
+    <row r="52" spans="1:34" ht="32.1" customHeight="1">
       <c r="A52" s="53" t="s">
         <v>59</v>
       </c>
@@ -4821,7 +4819,7 @@
         <v>00000FF</v>
       </c>
     </row>
-    <row r="57" spans="1:34" ht="32.15" customHeight="1">
+    <row r="57" spans="1:34" ht="32.1" customHeight="1">
       <c r="A57" s="53" t="s">
         <v>63</v>
       </c>
@@ -5165,7 +5163,7 @@
         <v>00000FF</v>
       </c>
     </row>
-    <row r="62" spans="1:34" ht="32.15" customHeight="1">
+    <row r="62" spans="1:34" ht="32.1" customHeight="1">
       <c r="A62" s="53" t="s">
         <v>67</v>
       </c>
@@ -5695,7 +5693,7 @@
         <v>00000FF</v>
       </c>
     </row>
-    <row r="69" spans="1:34" ht="32.15" customHeight="1">
+    <row r="69" spans="1:34" ht="32.1" customHeight="1">
       <c r="A69" s="46" t="s">
         <v>73</v>
       </c>
@@ -5853,7 +5851,7 @@
         <v>000000F</v>
       </c>
     </row>
-    <row r="72" spans="1:34" ht="31">
+    <row r="72" spans="1:34" ht="31.2">
       <c r="A72" s="27" t="s">
         <v>74</v>
       </c>
@@ -5887,7 +5885,7 @@
       <c r="AC72" s="19"/>
       <c r="AD72" s="20"/>
     </row>
-    <row r="73" spans="1:34" ht="31">
+    <row r="73" spans="1:34" ht="31.2">
       <c r="A73" s="28"/>
       <c r="B73" s="29"/>
       <c r="C73" s="11"/>
@@ -6028,7 +6026,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" s="11">
         <v>1</v>
@@ -6104,7 +6102,7 @@
       </c>
       <c r="AH75" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C75:F75), 1), BIN2HEX(_xlfn.CONCAT(G75:N75), 2), BIN2HEX(_xlfn.CONCAT(O75:V75), 2), BIN2HEX(_xlfn.CONCAT(W75:AD75), 2) )</f>
-        <v>8842C1F</v>
+        <v>9842C1F</v>
       </c>
     </row>
     <row r="76" spans="1:34">
@@ -6213,10 +6211,10 @@
         <v>0</v>
       </c>
       <c r="E77" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="11">
         <v>0</v>
@@ -6270,7 +6268,7 @@
         <v>1</v>
       </c>
       <c r="X77" s="69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y77" s="31">
         <v>1</v>
@@ -6292,7 +6290,7 @@
       </c>
       <c r="AH77" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C77:F77), 1), BIN2HEX(_xlfn.CONCAT(G77:N77), 2), BIN2HEX(_xlfn.CONCAT(O77:V77), 2), BIN2HEX(_xlfn.CONCAT(W77:AD77), 2) )</f>
-        <v>00000FF</v>
+        <v>30000BF</v>
       </c>
     </row>
     <row r="78" spans="1:34">
@@ -6327,7 +6325,7 @@
       <c r="AC78" s="31"/>
       <c r="AD78" s="21"/>
     </row>
-    <row r="79" spans="1:34" ht="31">
+    <row r="79" spans="1:34" ht="31.2">
       <c r="A79" s="27" t="s">
         <v>79</v>
       </c>
@@ -6361,7 +6359,7 @@
       <c r="AC79" s="19"/>
       <c r="AD79" s="20"/>
     </row>
-    <row r="80" spans="1:34" ht="31">
+    <row r="80" spans="1:34" ht="31.2">
       <c r="A80" s="28"/>
       <c r="B80" s="29"/>
       <c r="C80" s="11"/>
@@ -6514,7 +6512,7 @@
         <v>0</v>
       </c>
       <c r="J82" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" s="13">
         <v>0</v>
@@ -6578,7 +6576,7 @@
       </c>
       <c r="AH82" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C82:F82), 1), BIN2HEX(_xlfn.CONCAT(G82:N82), 2), BIN2HEX(_xlfn.CONCAT(O82:V82), 2), BIN2HEX(_xlfn.CONCAT(W82:AD82), 2) )</f>
-        <v>4100095</v>
+        <v>4000095</v>
       </c>
     </row>
     <row r="83" spans="1:36">
@@ -6702,7 +6700,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" s="13">
         <v>0</v>
@@ -6766,7 +6764,7 @@
       </c>
       <c r="AH84" t="str">
         <f t="shared" ref="AH84:AH85" si="4">_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C84:F84), 1), BIN2HEX(_xlfn.CONCAT(G84:N84), 2), BIN2HEX(_xlfn.CONCAT(O84:V84), 2), BIN2HEX(_xlfn.CONCAT(W84:AD84), 2) )</f>
-        <v>410009C</v>
+        <v>400009C</v>
       </c>
       <c r="AI84" s="5"/>
       <c r="AJ84" s="5"/>
@@ -6798,19 +6796,19 @@
         <v>0</v>
       </c>
       <c r="J85" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="13">
         <v>0</v>
       </c>
       <c r="M85" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" s="26">
         <v>0</v>
@@ -6819,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="Q85" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" s="15">
         <v>0</v>
@@ -6862,7 +6860,7 @@
       </c>
       <c r="AH85" t="str">
         <f t="shared" si="4"/>
-        <v>04A003F</v>
+        <v>051203F</v>
       </c>
       <c r="AI85" s="5"/>
       <c r="AJ85" s="5"/>
@@ -6909,10 +6907,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F64"/>
-  <sheetFormatPr defaultColWidth="11.08203125" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="10.58203125" customWidth="1"/>
+    <col min="6" max="6" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7123,7 +7121,7 @@
       </c>
       <c r="D13" s="6" t="str">
         <f>microcode!AH23</f>
-        <v>049783F</v>
+        <v>04A633F</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -7155,7 +7153,7 @@
       </c>
       <c r="D15" s="6" t="str">
         <f>microcode!AH48</f>
-        <v>1040C3F</v>
+        <v>104143F</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7203,7 +7201,7 @@
       </c>
       <c r="D18" s="6" t="str">
         <f>microcode!AH82</f>
-        <v>4100095</v>
+        <v>4000095</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -7238,7 +7236,7 @@
         <v>4080323</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="17">
+    <row r="21" spans="1:5" ht="17.399999999999999">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -7332,7 +7330,7 @@
       </c>
       <c r="D26" s="6" t="str">
         <f>microcode!AH84</f>
-        <v>410009C</v>
+        <v>400009C</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7380,7 +7378,7 @@
       </c>
       <c r="D29" s="6" t="str">
         <f>microcode!AH85</f>
-        <v>04A003F</v>
+        <v>051203F</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -7412,7 +7410,7 @@
       </c>
       <c r="D31" s="6" t="str">
         <f>microcode!AH75</f>
-        <v>8842C1F</v>
+        <v>9842C1F</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7459,7 +7457,7 @@
       </c>
       <c r="D34" s="6" t="str">
         <f>microcode!AH77</f>
-        <v>00000FF</v>
+        <v>30000BF</v>
       </c>
     </row>
     <row r="35" spans="1:4">

--- a/hw04/hw04/microcode.xlsx
+++ b/hw04/hw04/microcode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruh\Documents\GT\Summer 2023\CS_2110\hw04\hw04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huan\Documents\GT\Summer 2023\CS_2110\hw04\hw04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D92551-0C40-45C2-846E-22BE8C6F3C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE95F03-373A-45B9-A07F-A85DE7DC0BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="microcode" sheetId="1" r:id="rId1"/>
@@ -1121,14 +1121,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BW86"/>
-  <sheetFormatPr defaultColWidth="11.296875" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="22.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="30" width="4.59765625" customWidth="1"/>
-    <col min="31" max="31" width="2.59765625" customWidth="1"/>
+    <col min="1" max="1" width="22.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="30" width="4.58203125" customWidth="1"/>
+    <col min="31" max="31" width="2.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75" ht="87">
+    <row r="1" spans="1:75" ht="88">
       <c r="A1" s="41"/>
       <c r="B1" s="42"/>
       <c r="C1" s="55" t="s">
@@ -1252,7 +1252,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:75" ht="32.1" customHeight="1">
+    <row r="3" spans="1:75" ht="32.15" customHeight="1">
       <c r="A3" s="46" t="s">
         <v>23</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>2100038</v>
       </c>
     </row>
-    <row r="8" spans="1:75" ht="32.1" customHeight="1">
+    <row r="8" spans="1:75" ht="32.15" customHeight="1">
       <c r="A8" s="27" t="s">
         <v>27</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>0000020</v>
       </c>
     </row>
-    <row r="11" spans="1:75" ht="32.1" customHeight="1">
+    <row r="11" spans="1:75" ht="32.15" customHeight="1">
       <c r="A11" s="46" t="s">
         <v>28</v>
       </c>
@@ -1790,7 +1790,7 @@
       <c r="AC11" s="19"/>
       <c r="AD11" s="20"/>
     </row>
-    <row r="12" spans="1:75" ht="16.05" customHeight="1">
+    <row r="12" spans="1:75" ht="16" customHeight="1">
       <c r="A12" s="51"/>
       <c r="C12" s="62"/>
       <c r="D12" s="62"/>
@@ -1952,7 +1952,7 @@
       <c r="BV13" s="4"/>
       <c r="BW13" s="4"/>
     </row>
-    <row r="14" spans="1:75" ht="32.1" customHeight="1">
+    <row r="14" spans="1:75" ht="32.15" customHeight="1">
       <c r="A14" s="46" t="s">
         <v>30</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>188413F</v>
       </c>
     </row>
-    <row r="17" spans="1:34" ht="32.1" customHeight="1">
+    <row r="17" spans="1:34" ht="32.15" customHeight="1">
       <c r="A17" s="46" t="s">
         <v>32</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>041103F</v>
       </c>
     </row>
-    <row r="21" spans="1:34" ht="32.1" customHeight="1">
+    <row r="21" spans="1:34" ht="32.15" customHeight="1">
       <c r="A21" s="52" t="s">
         <v>35</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>04A633F</v>
       </c>
     </row>
-    <row r="24" spans="1:34" ht="32.1" customHeight="1">
+    <row r="24" spans="1:34" ht="32.15" customHeight="1">
       <c r="A24" s="46" t="s">
         <v>37</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>161E03F</v>
       </c>
     </row>
-    <row r="29" spans="1:34" ht="32.1" customHeight="1">
+    <row r="29" spans="1:34" ht="32.15" customHeight="1">
       <c r="A29" s="46" t="s">
         <v>41</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>190003F</v>
       </c>
     </row>
-    <row r="34" spans="1:34" ht="32.1" customHeight="1">
+    <row r="34" spans="1:34" ht="32.15" customHeight="1">
       <c r="A34" s="46" t="s">
         <v>45</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>190003F</v>
       </c>
     </row>
-    <row r="41" spans="1:34" ht="32.1" customHeight="1">
+    <row r="41" spans="1:34" ht="32.15" customHeight="1">
       <c r="A41" s="46" t="s">
         <v>51</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>190003F</v>
       </c>
     </row>
-    <row r="46" spans="1:34" ht="32.1" customHeight="1">
+    <row r="46" spans="1:34" ht="32.15" customHeight="1">
       <c r="A46" s="46" t="s">
         <v>55</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>104143F</v>
       </c>
     </row>
-    <row r="49" spans="1:34" ht="32.1" customHeight="1">
+    <row r="49" spans="1:34" ht="32.15" customHeight="1">
       <c r="A49" s="46" t="s">
         <v>57</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>188423F</v>
       </c>
     </row>
-    <row r="52" spans="1:34" ht="32.1" customHeight="1">
+    <row r="52" spans="1:34" ht="32.15" customHeight="1">
       <c r="A52" s="53" t="s">
         <v>59</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>00000FF</v>
       </c>
     </row>
-    <row r="57" spans="1:34" ht="32.1" customHeight="1">
+    <row r="57" spans="1:34" ht="32.15" customHeight="1">
       <c r="A57" s="53" t="s">
         <v>63</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>00000FF</v>
       </c>
     </row>
-    <row r="62" spans="1:34" ht="32.1" customHeight="1">
+    <row r="62" spans="1:34" ht="32.15" customHeight="1">
       <c r="A62" s="53" t="s">
         <v>67</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>00000FF</v>
       </c>
     </row>
-    <row r="69" spans="1:34" ht="32.1" customHeight="1">
+    <row r="69" spans="1:34" ht="32.15" customHeight="1">
       <c r="A69" s="46" t="s">
         <v>73</v>
       </c>
@@ -5851,7 +5851,7 @@
         <v>000000F</v>
       </c>
     </row>
-    <row r="72" spans="1:34" ht="31.2">
+    <row r="72" spans="1:34" ht="31">
       <c r="A72" s="27" t="s">
         <v>74</v>
       </c>
@@ -5885,7 +5885,7 @@
       <c r="AC72" s="19"/>
       <c r="AD72" s="20"/>
     </row>
-    <row r="73" spans="1:34" ht="31.2">
+    <row r="73" spans="1:34" ht="31">
       <c r="A73" s="28"/>
       <c r="B73" s="29"/>
       <c r="C73" s="11"/>
@@ -6325,7 +6325,7 @@
       <c r="AC78" s="31"/>
       <c r="AD78" s="21"/>
     </row>
-    <row r="79" spans="1:34" ht="31.2">
+    <row r="79" spans="1:34" ht="31">
       <c r="A79" s="27" t="s">
         <v>79</v>
       </c>
@@ -6359,7 +6359,7 @@
       <c r="AC79" s="19"/>
       <c r="AD79" s="20"/>
     </row>
-    <row r="80" spans="1:34" ht="31.2">
+    <row r="80" spans="1:34" ht="31">
       <c r="A80" s="28"/>
       <c r="B80" s="29"/>
       <c r="C80" s="11"/>
@@ -6805,10 +6805,10 @@
         <v>0</v>
       </c>
       <c r="M85" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" s="26">
         <v>0</v>
@@ -6817,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="Q85" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" s="15">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="AH85" t="str">
         <f t="shared" si="4"/>
-        <v>051203F</v>
+        <v>052003F</v>
       </c>
       <c r="AI85" s="5"/>
       <c r="AJ85" s="5"/>
@@ -6907,10 +6907,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F64"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.08203125" defaultRowHeight="15.5"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="10.59765625" customWidth="1"/>
+    <col min="6" max="6" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7236,7 +7236,7 @@
         <v>4080323</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="17.399999999999999">
+    <row r="21" spans="1:5" ht="17">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="D29" s="6" t="str">
         <f>microcode!AH85</f>
-        <v>051203F</v>
+        <v>052003F</v>
       </c>
     </row>
     <row r="30" spans="1:5">
